--- a/LC_Service_history_FINAL.xlsx
+++ b/LC_Service_history_FINAL.xlsx
@@ -600,7 +600,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H316"/>
+  <dimension ref="A1:I316"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14"/>
   <cols>
     <col width="13.59765625" customWidth="1" style="2" min="1" max="1"/>
@@ -651,6 +651,11 @@
           <t>Notes</t>
         </is>
       </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>CONVENTION (Neil, 10 Jul 2026): Cost 0 = line item included in the parent invoice row above; the parent row carries the full invoice amount.</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="n">
@@ -682,6 +687,11 @@
           <t>Dyno: 96kw; 285Nm</t>
         </is>
       </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>CLASSIFICATION RULE (rule-based, 10 Jul 2026): category beginning 'Manufacturers service' or 'In between service' = SCHEDULED; all else (incl. Pre-trip inspection) = UNSCHEDULED/RENEWAL. Rule applied in R8 dashboard JSON generation.</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="n">
@@ -701,7 +711,7 @@
         </is>
       </c>
       <c r="E3" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F3" s="1" t="inlineStr">
         <is>
@@ -753,7 +763,7 @@
         </is>
       </c>
       <c r="E5" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F5" s="1" t="inlineStr">
         <is>
@@ -779,7 +789,7 @@
         </is>
       </c>
       <c r="E6" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F6" s="1" t="inlineStr">
         <is>
@@ -831,7 +841,7 @@
         </is>
       </c>
       <c r="E8" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F8" s="1" t="inlineStr">
         <is>
@@ -883,7 +893,7 @@
         </is>
       </c>
       <c r="E10" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F10" s="1" t="inlineStr">
         <is>
@@ -909,7 +919,7 @@
         </is>
       </c>
       <c r="E11" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F11" s="1" t="inlineStr">
         <is>
@@ -935,7 +945,7 @@
         </is>
       </c>
       <c r="E12" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F12" s="1" t="inlineStr">
         <is>
@@ -961,7 +971,7 @@
         </is>
       </c>
       <c r="E13" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F13" s="1" t="inlineStr">
         <is>
@@ -1013,7 +1023,7 @@
         </is>
       </c>
       <c r="E15" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F15" s="1" t="inlineStr">
         <is>
@@ -1091,7 +1101,7 @@
         </is>
       </c>
       <c r="E18" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F18" s="1" t="inlineStr">
         <is>
@@ -1117,7 +1127,7 @@
         </is>
       </c>
       <c r="E19" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F19" s="1" t="inlineStr">
         <is>
@@ -1143,7 +1153,7 @@
         </is>
       </c>
       <c r="E20" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F20" s="1" t="inlineStr">
         <is>
@@ -1169,7 +1179,7 @@
         </is>
       </c>
       <c r="E21" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F21" s="1" t="inlineStr">
         <is>
@@ -1247,7 +1257,7 @@
         </is>
       </c>
       <c r="E24" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F24" s="1" t="inlineStr">
         <is>
@@ -1273,7 +1283,7 @@
         </is>
       </c>
       <c r="E25" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F25" s="1" t="inlineStr">
         <is>
@@ -1299,7 +1309,7 @@
         </is>
       </c>
       <c r="E26" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F26" s="1" t="inlineStr">
         <is>
@@ -1325,7 +1335,7 @@
         </is>
       </c>
       <c r="E27" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F27" s="1" t="inlineStr">
         <is>
@@ -1351,7 +1361,7 @@
         </is>
       </c>
       <c r="E28" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F28" s="1" t="inlineStr">
         <is>
@@ -1429,7 +1439,7 @@
         </is>
       </c>
       <c r="E31" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F31" s="1" t="inlineStr">
         <is>
@@ -1533,7 +1543,7 @@
         </is>
       </c>
       <c r="E35" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F35" s="1" t="inlineStr">
         <is>
@@ -1559,7 +1569,7 @@
         </is>
       </c>
       <c r="E36" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F36" s="1" t="inlineStr">
         <is>
@@ -1585,7 +1595,7 @@
         </is>
       </c>
       <c r="E37" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F37" s="1" t="inlineStr">
         <is>
@@ -1611,7 +1621,7 @@
         </is>
       </c>
       <c r="E38" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F38" s="1" t="inlineStr">
         <is>
@@ -1637,7 +1647,7 @@
         </is>
       </c>
       <c r="E39" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F39" s="1" t="inlineStr">
         <is>
@@ -1715,7 +1725,7 @@
         </is>
       </c>
       <c r="E42" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F42" s="1" t="inlineStr">
         <is>
@@ -1793,7 +1803,7 @@
         </is>
       </c>
       <c r="E45" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F45" s="1" t="inlineStr">
         <is>
@@ -1819,7 +1829,7 @@
         </is>
       </c>
       <c r="E46" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F46" s="1" t="inlineStr">
         <is>
@@ -1871,7 +1881,7 @@
         </is>
       </c>
       <c r="E48" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F48" s="1" t="inlineStr">
         <is>
@@ -2032,7 +2042,7 @@
         </is>
       </c>
       <c r="E54" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F54" s="1" t="inlineStr">
         <is>
@@ -2058,7 +2068,7 @@
         </is>
       </c>
       <c r="E55" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F55" s="1" t="inlineStr">
         <is>
@@ -2084,7 +2094,7 @@
         </is>
       </c>
       <c r="E56" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F56" s="1" t="inlineStr">
         <is>
@@ -2110,7 +2120,7 @@
         </is>
       </c>
       <c r="E57" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F57" s="1" t="inlineStr">
         <is>
@@ -2136,7 +2146,7 @@
         </is>
       </c>
       <c r="E58" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F58" s="1" t="inlineStr">
         <is>
@@ -2162,7 +2172,7 @@
         </is>
       </c>
       <c r="E59" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F59" s="1" t="inlineStr">
         <is>

--- a/LC_Service_history_FINAL.xlsx
+++ b/LC_Service_history_FINAL.xlsx
@@ -7,6 +7,7 @@
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Services" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Advisories" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Services'!$A$1:$G$289</definedName>
@@ -9072,4 +9073,670 @@
     <brk id="80" min="0" max="16383" man="1"/>
   </rowBreaks>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:J13"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="10" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="10" customWidth="1" min="3" max="3"/>
+    <col width="16" customWidth="1" min="4" max="4"/>
+    <col width="34" customWidth="1" min="5" max="5"/>
+    <col width="60" customWidth="1" min="6" max="6"/>
+    <col width="10" customWidth="1" min="7" max="7"/>
+    <col width="52" customWidth="1" min="8" max="8"/>
+    <col width="10" customWidth="1" min="9" max="9"/>
+    <col width="9" customWidth="1" min="10" max="10"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="11" t="inlineStr">
+        <is>
+          <t>ID</t>
+        </is>
+      </c>
+      <c r="B1" s="26" t="inlineStr">
+        <is>
+          <t>Date raised</t>
+        </is>
+      </c>
+      <c r="C1" s="9" t="inlineStr">
+        <is>
+          <t>Mileage</t>
+        </is>
+      </c>
+      <c r="D1" s="9" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
+      <c r="E1" s="10" t="inlineStr">
+        <is>
+          <t>Item</t>
+        </is>
+      </c>
+      <c r="F1" s="9" t="inlineStr">
+        <is>
+          <t>Detail</t>
+        </is>
+      </c>
+      <c r="G1" s="9" t="inlineStr">
+        <is>
+          <t>Severity</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>Action</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+      <c r="J1" s="11" t="inlineStr">
+        <is>
+          <t>OI ref</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>ADV-001</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+      <c r="C2" t="n">
+        <v>308248</v>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>PW Auto Centre</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>Rear hub seal weeping</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Hub seal weeping; risk of gear oil tracking onto rear brake shoes. Rear drums are the primary parking brake — oil-contaminated shoes lose friction entirely. Shoes replaced Jan 2026 @ 293,949 km.</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>Confirm which side. Check both rear drums for contamination. Wet shoe = immediate seal + shoe replacement, do not drive.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>OI-61</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>ADV-002</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
+        <v>308248</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>PW Auto Centre</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>Front knuckle grease leak</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Birfield CV joints run inside the knuckle housing packed with grease. Loss of grease means the birfield runs dry; wear then accelerates to CV failure. Knuckle kit replaced Feb 2025 @ 271,200 km.</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>Confirm side. Re-pack with molybdenum disulphide birfield grease, inspect seal face, replace seal if damaged. Do not leave for the field.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>OI-61</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>ADV-003</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>308248</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>PW Auto Centre</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Water pump — no replacement record</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>No replacement on record in 316 service entries. Weep hole dry at 308,248 km and again at 308,500 km.</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Replace proactively; bundle with timing belt (RA-3) and thermostat at the same rocker-cover-off visit.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>OI-62</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>ADV-004</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>2024-11</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>264347</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>PW Auto Centre</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Radiator quality flagged at install</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Replaced Nov 2024 @ 264,347 km by G-Tec (R10,149). Quality flagged as poor by PW at the time.</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Monitor. Budget for heavy-duty replacement before the expedition. Feeds RA-5.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>OI-6</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>ADV-006</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>308248</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>R8 analysis</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Thermostat — no record</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>No thermostat replacement on record. Stuck-closed thermostat is a top-three 1HZ overheating cause. 82degC OEM spec — do not fit lower-temperature variants.</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Replace at next workshop visit. Combine with coolant flush and pressure test. Carry removed unit as field spare.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>OI-62</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>ADV-007</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>308248</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>R8 analysis</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Wheel bearing repack overdue</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Bearings replaced Feb 2025 @ 271,200 km but last repack ~245,000 km. Severe-use interval is 20,000 km — approximately 63,684 km overdue.</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>Front + rear repack with Toyota-spec grease. Inspect seals. Combine with brake inspection and ADV-001.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>OI-63</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>ADV-008</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>R8 analysis</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Diff breather extensions — status unknown</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Standard Toyota breathers are inadequate for water crossings above ankle depth. Extended breathers route front diff, rear diff and transfer vents high in the engine bay. Cross-ref R31 S3 item 7.</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>Visual check at next service. Fit before any expedition water crossings if absent.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>OI-64</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>ADV-009</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>308248</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>R8 analysis</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Coolant flush overdue</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Only one flush on record — Aug 2023 @ 224,406 km. Approximately 86,006 km overdue.</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>Schedule before the expedition; bundle with thermostat and pressure test.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>OI-62</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>ADV-010</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
+        <v>308248</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>PW Auto Centre</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Boost pipe clamp condition unconfirmed</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Visual check only at Apr 2026 service; clamp condition not confirmed. A boost leak drops power and raises EGT.</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Inspect at next service (~315,000 km).</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>OI-7</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>ADV-011</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>R8 supplement (Service Checklist)</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Rocker cover gasket + half-moon seal — replace</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Flagged CRITICAL. First and most cost-effective intervention for the cylinder head oil seepage monitor. Genuine Toyota rocker cover gasket + front/rear grommets + reseal half-moon plug (11183-54011).</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Combine with tappet inspection — the rocker cover is already off at that event, and again at the RA-3 timing belt.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>OI-66</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>ADV-012</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>R8 supplement (Service Checklist)</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>PCV / crankcase breather routing — verify</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Flagged CRITICAL. If the breather is routed post-intercooler rather than pre-turbo, boost can back-pressurise the crankcase and force oil out at every top-end seal — which would directly explain the head seepage. Never verified.</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>Trace the breather hose from valve cover to intake at the next visit to a 1HZ-experienced workshop. Diagnose BEFORE replacing the rocker gasket, or the gasket may simply fail again.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>OI-66</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>ADV-013</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>R8 supplement (Service Checklist)</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Racor fuel pre-filter — fit before expedition</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Flagged as a pre-expedition fitment. Relevant given the Jun 2026 fuel contamination event: tank dropped, flushed and the filter housing renewed at 310,412 km.</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>Specify and fit during the pre-departure push. Sits with the R31 Tier 2 items in R8 timeline.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>OI-11</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/LC_Service_history_FINAL.xlsx
+++ b/LC_Service_history_FINAL.xlsx
@@ -9591,7 +9591,7 @@
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>OI-7</t>
+          <t>OI-75</t>
         </is>
       </c>
     </row>

--- a/LC_Service_history_FINAL.xlsx
+++ b/LC_Service_history_FINAL.xlsx
@@ -19,9 +19,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
+  <numFmts count="3">
     <numFmt numFmtId="164" formatCode="&quot;R&quot;#,##0.00"/>
     <numFmt numFmtId="165" formatCode="&quot;R&quot;#,##0_);[Red]\(&quot;R&quot;#,##0\)"/>
+    <numFmt numFmtId="166" formatCode="yyyy-mm-dd h:mm:ss"/>
   </numFmts>
   <fonts count="5">
     <font>
@@ -601,7 +602,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I316"/>
+  <dimension ref="A1:I317"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14"/>
   <cols>
     <col width="13.59765625" customWidth="1" style="2" min="1" max="1"/>
@@ -9054,6 +9055,35 @@
       <c r="G316" t="inlineStr">
         <is>
           <t>Per quote LC76SW004 — invoice date &amp; final cost TO CONFIRM. Enertec Power+ 210Ah LiFePO4 house battery; Victron Orion 12/12-50 DC-DC (~40A cap); MultiPlus 12/500/20-16; SmartSolar MPPT 100/30; SmartShunt 500A; BatteryProtect 65A; Safety Hub 150 + battery switch; 16A shore inlet; DEFA removed. Willard 650 crank unchanged.</t>
+        </is>
+      </c>
+    </row>
+    <row r="317">
+      <c r="A317" s="2" t="n">
+        <v>46238</v>
+      </c>
+      <c r="B317" s="27" t="n">
+        <v>311263</v>
+      </c>
+      <c r="C317" s="1" t="inlineStr">
+        <is>
+          <t>Battery - starter</t>
+        </is>
+      </c>
+      <c r="D317" t="inlineStr">
+        <is>
+          <t>Battery</t>
+        </is>
+      </c>
+      <c r="E317" s="3" t="inlineStr">
+        <is>
+          <t>TBC</t>
+        </is>
+      </c>
+      <c r="F317" s="1" t="n"/>
+      <c r="G317" t="inlineStr">
+        <is>
+          <t>Enertec 650B-BLS Premium Plus Silver — SMF (sealed calcium), 92 Ah, 750 CCA SAE / 680 EN. Replaced the Willard 650 (fitted 23 Jan 2025 @ 271,056 km). Cost TO CONFIRM.</t>
         </is>
       </c>
     </row>

--- a/LC_Service_history_FINAL.xlsx
+++ b/LC_Service_history_FINAL.xlsx
@@ -8,11 +8,9 @@
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Services" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Advisories" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Build_Accessories" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
-  <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Services'!$A$1:$G$289</definedName>
-    <definedName name="_xlnm.Print_Titles" localSheetId="0">'Services'!$1:$1</definedName>
-  </definedNames>
+  <definedNames/>
   <calcPr calcId="0" fullCalcOnLoad="1"/>
 </workbook>
 </file>
@@ -24,7 +22,7 @@
     <numFmt numFmtId="165" formatCode="&quot;R&quot;#,##0_);[Red]\(&quot;R&quot;#,##0\)"/>
     <numFmt numFmtId="166" formatCode="yyyy-mm-dd h:mm:ss"/>
   </numFmts>
-  <fonts count="5">
+  <fonts count="8">
     <font>
       <name val="Arial Narrow"/>
       <family val="2"/>
@@ -57,8 +55,23 @@
       <color theme="1"/>
       <sz val="10"/>
     </font>
+    <font>
+      <name val="Arial Narrow"/>
+      <b val="1"/>
+      <color rgb="FFFFFFFF"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Arial Narrow"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Arial Narrow"/>
+      <i val="1"/>
+      <sz val="9"/>
+    </font>
   </fonts>
-  <fills count="7">
+  <fills count="8">
     <fill>
       <patternFill/>
     </fill>
@@ -93,6 +106,11 @@
       <patternFill patternType="solid">
         <fgColor theme="4" tint="0.5999938962981048"/>
         <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF002060"/>
       </patternFill>
     </fill>
   </fills>
@@ -156,7 +174,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="38">
+  <cellXfs count="46">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="14" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -225,6 +243,16 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="165" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="14" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="37" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -602,19 +630,19 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I317"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14"/>
+  <dimension ref="A1:I310"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="13.59765625" customWidth="1" style="2" min="1" max="1"/>
-    <col width="11" customWidth="1" style="27" min="2" max="2"/>
-    <col width="48.796875" bestFit="1" customWidth="1" style="1" min="3" max="3"/>
-    <col width="31" bestFit="1" customWidth="1" style="1" min="4" max="4"/>
-    <col width="12" bestFit="1" customWidth="1" style="3" min="5" max="5"/>
-    <col width="24.59765625" customWidth="1" style="1" min="6" max="6"/>
-    <col width="62.3984375" customWidth="1" style="32" min="7" max="7"/>
-    <col width="13.19921875" customWidth="1" style="1" min="8" max="8"/>
-    <col width="11" customWidth="1" style="1" min="9" max="9"/>
-    <col width="11" customWidth="1" style="1" min="10" max="16384"/>
+    <col width="13.59765625" customWidth="1" min="1" max="1"/>
+    <col width="11" customWidth="1" min="2" max="2"/>
+    <col width="48.796875" customWidth="1" min="3" max="3"/>
+    <col width="31" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="24.59765625" customWidth="1" min="6" max="6"/>
+    <col width="62.3984375" customWidth="1" min="7" max="7"/>
+    <col width="13.19921875" customWidth="1" min="8" max="8"/>
+    <col width="11" customWidth="1" min="9" max="9"/>
+    <col width="11" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -4762,27 +4790,27 @@
     </row>
     <row r="158">
       <c r="A158" s="2" t="n">
-        <v>45593</v>
+        <v>45601</v>
       </c>
       <c r="B158" s="27" t="n">
-        <v>262000</v>
+        <v>264005</v>
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>Multi Media Unit (Mid Spect TT) with Butterfly camera</t>
+          <t>Rear door rubbers</t>
         </is>
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>Infotainment</t>
+          <t>Door rubbers</t>
         </is>
       </c>
       <c r="E158" s="3" t="n">
-        <v>7000</v>
+        <v>7767</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>Musical Cars</t>
+          <t>Toyota Tokai</t>
         </is>
       </c>
     </row>
@@ -4795,16 +4823,16 @@
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>Rear door rubbers</t>
+          <t>Antenna</t>
         </is>
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>Door rubbers</t>
+          <t>Antenna</t>
         </is>
       </c>
       <c r="E159" s="3" t="n">
-        <v>7767</v>
+        <v>2182</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -4813,59 +4841,59 @@
       </c>
     </row>
     <row r="160">
-      <c r="A160" s="2" t="n">
-        <v>45601</v>
-      </c>
-      <c r="B160" s="27" t="n">
-        <v>264005</v>
-      </c>
-      <c r="C160" t="inlineStr">
-        <is>
-          <t>Antenna</t>
-        </is>
-      </c>
-      <c r="D160" t="inlineStr">
-        <is>
-          <t>Antenna</t>
-        </is>
-      </c>
-      <c r="E160" s="3" t="n">
-        <v>2182</v>
-      </c>
-      <c r="F160" t="inlineStr">
-        <is>
-          <t>Toyota Tokai</t>
+      <c r="A160" s="4" t="n">
+        <v>45608</v>
+      </c>
+      <c r="B160" s="28" t="n">
+        <v>263000</v>
+      </c>
+      <c r="C160" s="5" t="inlineStr">
+        <is>
+          <t>Maxxis AT811-03 (4)</t>
+        </is>
+      </c>
+      <c r="D160" s="5" t="inlineStr">
+        <is>
+          <t>Tyres</t>
+        </is>
+      </c>
+      <c r="E160" s="6" t="n">
+        <v>21873</v>
+      </c>
+      <c r="F160" s="5" t="inlineStr">
+        <is>
+          <t>First Alignment</t>
+        </is>
+      </c>
+      <c r="G160" s="32" t="inlineStr">
+        <is>
+          <t>48,000 km on BFG's</t>
         </is>
       </c>
     </row>
     <row r="161">
-      <c r="A161" s="4" t="n">
-        <v>45608</v>
-      </c>
-      <c r="B161" s="28" t="n">
-        <v>263000</v>
-      </c>
-      <c r="C161" s="5" t="inlineStr">
-        <is>
-          <t>Maxxis AT811-03 (4)</t>
-        </is>
-      </c>
-      <c r="D161" s="5" t="inlineStr">
-        <is>
-          <t>Tyres</t>
-        </is>
-      </c>
-      <c r="E161" s="6" t="n">
-        <v>21873</v>
-      </c>
-      <c r="F161" s="5" t="inlineStr">
-        <is>
-          <t>First Alignment</t>
-        </is>
-      </c>
-      <c r="G161" s="32" t="inlineStr">
-        <is>
-          <t>48,000 km on BFG's</t>
+      <c r="A161" s="2" t="n">
+        <v>45610</v>
+      </c>
+      <c r="B161" s="27" t="n">
+        <v>263500</v>
+      </c>
+      <c r="C161" s="1" t="inlineStr">
+        <is>
+          <t>Stud extraction (bolt in Turbo)</t>
+        </is>
+      </c>
+      <c r="D161" s="1" t="inlineStr">
+        <is>
+          <t>Turbo</t>
+        </is>
+      </c>
+      <c r="E161" s="3" t="n">
+        <v>1500</v>
+      </c>
+      <c r="F161" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Powerflow Exhausts </t>
         </is>
       </c>
     </row>
@@ -4878,7 +4906,7 @@
       </c>
       <c r="C162" s="1" t="inlineStr">
         <is>
-          <t>Stud extraction (bolt in Turbo)</t>
+          <t>Flange - turbo &amp; exhaust</t>
         </is>
       </c>
       <c r="D162" s="1" t="inlineStr">
@@ -4887,7 +4915,7 @@
         </is>
       </c>
       <c r="E162" s="3" t="n">
-        <v>1500</v>
+        <v>1200</v>
       </c>
       <c r="F162" s="1" t="inlineStr">
         <is>
@@ -4897,27 +4925,27 @@
     </row>
     <row r="163">
       <c r="A163" s="2" t="n">
-        <v>45610</v>
+        <v>45611</v>
       </c>
       <c r="B163" s="27" t="n">
-        <v>263500</v>
+        <v>264347</v>
       </c>
       <c r="C163" s="1" t="inlineStr">
         <is>
-          <t>Flange - turbo &amp; exhaust</t>
+          <t>Service 265,000 km</t>
         </is>
       </c>
       <c r="D163" s="1" t="inlineStr">
         <is>
-          <t>Turbo</t>
+          <t>Manufacturers service 265,000 km</t>
         </is>
       </c>
       <c r="E163" s="3" t="n">
-        <v>1200</v>
+        <v>5893</v>
       </c>
       <c r="F163" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Powerflow Exhausts </t>
+          <t>G-Tec</t>
         </is>
       </c>
     </row>
@@ -4930,16 +4958,16 @@
       </c>
       <c r="C164" s="1" t="inlineStr">
         <is>
-          <t>Service 265,000 km</t>
+          <t>Turbo pipe</t>
         </is>
       </c>
       <c r="D164" s="1" t="inlineStr">
         <is>
-          <t>Manufacturers service 265,000 km</t>
+          <t>Turbo</t>
         </is>
       </c>
       <c r="E164" s="3" t="n">
-        <v>5893</v>
+        <v>1173</v>
       </c>
       <c r="F164" s="1" t="inlineStr">
         <is>
@@ -4956,16 +4984,16 @@
       </c>
       <c r="C165" s="1" t="inlineStr">
         <is>
-          <t>Turbo pipe</t>
+          <t>Radiator</t>
         </is>
       </c>
       <c r="D165" s="1" t="inlineStr">
         <is>
-          <t>Turbo</t>
+          <t>Cooling system</t>
         </is>
       </c>
       <c r="E165" s="3" t="n">
-        <v>1173</v>
+        <v>10149</v>
       </c>
       <c r="F165" s="1" t="inlineStr">
         <is>
@@ -4975,23 +5003,23 @@
     </row>
     <row r="166">
       <c r="A166" s="2" t="n">
-        <v>45611</v>
+        <v>45680</v>
       </c>
       <c r="B166" s="27" t="n">
-        <v>264347</v>
+        <v>271056</v>
       </c>
       <c r="C166" s="1" t="inlineStr">
         <is>
-          <t>Radiator</t>
+          <t>Service 270,000 km</t>
         </is>
       </c>
       <c r="D166" s="1" t="inlineStr">
         <is>
-          <t>Cooling system</t>
+          <t>Manufacturers service 270,000 km</t>
         </is>
       </c>
       <c r="E166" s="3" t="n">
-        <v>10149</v>
+        <v>5853</v>
       </c>
       <c r="F166" s="1" t="inlineStr">
         <is>
@@ -5008,16 +5036,16 @@
       </c>
       <c r="C167" s="1" t="inlineStr">
         <is>
-          <t>Service 270,000 km</t>
+          <t>Fan belt kit</t>
         </is>
       </c>
       <c r="D167" s="1" t="inlineStr">
         <is>
-          <t>Manufacturers service 270,000 km</t>
+          <t>Fan belt</t>
         </is>
       </c>
       <c r="E167" s="3" t="n">
-        <v>5853</v>
+        <v>1131</v>
       </c>
       <c r="F167" s="1" t="inlineStr">
         <is>
@@ -5034,16 +5062,16 @@
       </c>
       <c r="C168" s="1" t="inlineStr">
         <is>
-          <t>Fan belt kit</t>
-        </is>
-      </c>
-      <c r="D168" s="1" t="inlineStr">
-        <is>
-          <t>Fan belt</t>
+          <t>Battery - starter</t>
+        </is>
+      </c>
+      <c r="D168" t="inlineStr">
+        <is>
+          <t>Battery</t>
         </is>
       </c>
       <c r="E168" s="3" t="n">
-        <v>1131</v>
+        <v>2975</v>
       </c>
       <c r="F168" s="1" t="inlineStr">
         <is>
@@ -5060,16 +5088,16 @@
       </c>
       <c r="C169" s="1" t="inlineStr">
         <is>
-          <t>Battery - starter</t>
-        </is>
-      </c>
-      <c r="D169" t="inlineStr">
+          <t>Battery - auxilary</t>
+        </is>
+      </c>
+      <c r="D169" s="1" t="inlineStr">
         <is>
           <t>Battery</t>
         </is>
       </c>
       <c r="E169" s="3" t="n">
-        <v>2975</v>
+        <v>3800</v>
       </c>
       <c r="F169" s="1" t="inlineStr">
         <is>
@@ -5079,27 +5107,32 @@
     </row>
     <row r="170">
       <c r="A170" s="2" t="n">
-        <v>45680</v>
+        <v>45701</v>
       </c>
       <c r="B170" s="27" t="n">
-        <v>271056</v>
+        <v>271200</v>
       </c>
       <c r="C170" s="1" t="inlineStr">
         <is>
-          <t>Battery - auxilary</t>
+          <t>Gearbox remove &amp; refit</t>
         </is>
       </c>
       <c r="D170" s="1" t="inlineStr">
         <is>
-          <t>Battery</t>
+          <t>Gearbox</t>
         </is>
       </c>
       <c r="E170" s="3" t="n">
-        <v>3800</v>
+        <v>3392</v>
       </c>
       <c r="F170" s="1" t="inlineStr">
         <is>
-          <t>G-Tec</t>
+          <t>Cape Transmissions</t>
+        </is>
+      </c>
+      <c r="G170" s="33" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Shudder on 5th gear - worn out parts </t>
         </is>
       </c>
     </row>
@@ -5110,9 +5143,9 @@
       <c r="B171" s="27" t="n">
         <v>271200</v>
       </c>
-      <c r="C171" s="1" t="inlineStr">
-        <is>
-          <t>Gearbox remove &amp; refit</t>
+      <c r="C171" t="inlineStr">
+        <is>
+          <t>Gearbox &amp; transfer bearing seal kit</t>
         </is>
       </c>
       <c r="D171" s="1" t="inlineStr">
@@ -5121,18 +5154,14 @@
         </is>
       </c>
       <c r="E171" s="3" t="n">
-        <v>3392</v>
+        <v>13124</v>
       </c>
       <c r="F171" s="1" t="inlineStr">
         <is>
           <t>Cape Transmissions</t>
         </is>
       </c>
-      <c r="G171" s="33" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Shudder on 5th gear - worn out parts </t>
-        </is>
-      </c>
+      <c r="G171" s="34" t="n"/>
     </row>
     <row r="172">
       <c r="A172" s="2" t="n">
@@ -5143,7 +5172,7 @@
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>Gearbox &amp; transfer bearing seal kit</t>
+          <t>Input shaft &amp; cluster gear</t>
         </is>
       </c>
       <c r="D172" s="1" t="inlineStr">
@@ -5152,7 +5181,7 @@
         </is>
       </c>
       <c r="E172" s="3" t="n">
-        <v>13124</v>
+        <v>6100</v>
       </c>
       <c r="F172" s="1" t="inlineStr">
         <is>
@@ -5170,7 +5199,7 @@
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>Input shaft &amp; cluster gear</t>
+          <t>Hub upgrade (3rd &amp; 4th)</t>
         </is>
       </c>
       <c r="D173" s="1" t="inlineStr">
@@ -5179,7 +5208,7 @@
         </is>
       </c>
       <c r="E173" s="3" t="n">
-        <v>6100</v>
+        <v>2351</v>
       </c>
       <c r="F173" s="1" t="inlineStr">
         <is>
@@ -5197,7 +5226,7 @@
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>Hub upgrade (3rd &amp; 4th)</t>
+          <t>Mainshaft / transfer input shaft upgraded</t>
         </is>
       </c>
       <c r="D174" s="1" t="inlineStr">
@@ -5206,7 +5235,7 @@
         </is>
       </c>
       <c r="E174" s="3" t="n">
-        <v>2351</v>
+        <v>10032</v>
       </c>
       <c r="F174" s="1" t="inlineStr">
         <is>
@@ -5224,7 +5253,7 @@
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>Mainshaft / transfer input shaft upgraded</t>
+          <t>Long spline transfer input gear upgraded</t>
         </is>
       </c>
       <c r="D175" s="1" t="inlineStr">
@@ -5233,7 +5262,7 @@
         </is>
       </c>
       <c r="E175" s="3" t="n">
-        <v>10032</v>
+        <v>2390</v>
       </c>
       <c r="F175" s="1" t="inlineStr">
         <is>
@@ -5251,7 +5280,7 @@
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>Long spline transfer input gear upgraded</t>
+          <t>5th Gear set upgrade</t>
         </is>
       </c>
       <c r="D176" s="1" t="inlineStr">
@@ -5260,7 +5289,7 @@
         </is>
       </c>
       <c r="E176" s="3" t="n">
-        <v>2390</v>
+        <v>4083</v>
       </c>
       <c r="F176" s="1" t="inlineStr">
         <is>
@@ -5278,7 +5307,7 @@
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>5th Gear set upgrade</t>
+          <t>Thrust washer 5th gear</t>
         </is>
       </c>
       <c r="D177" s="1" t="inlineStr">
@@ -5287,7 +5316,7 @@
         </is>
       </c>
       <c r="E177" s="3" t="n">
-        <v>4083</v>
+        <v>874</v>
       </c>
       <c r="F177" s="1" t="inlineStr">
         <is>
@@ -5305,7 +5334,7 @@
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>Thrust washer 5th gear</t>
+          <t>Spacer (hardend) 5th gear</t>
         </is>
       </c>
       <c r="D178" s="1" t="inlineStr">
@@ -5314,7 +5343,7 @@
         </is>
       </c>
       <c r="E178" s="3" t="n">
-        <v>874</v>
+        <v>692</v>
       </c>
       <c r="F178" s="1" t="inlineStr">
         <is>
@@ -5332,7 +5361,7 @@
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>Spacer (hardend) 5th gear</t>
+          <t>Oil gearbox</t>
         </is>
       </c>
       <c r="D179" s="1" t="inlineStr">
@@ -5341,7 +5370,7 @@
         </is>
       </c>
       <c r="E179" s="3" t="n">
-        <v>692</v>
+        <v>1524</v>
       </c>
       <c r="F179" s="1" t="inlineStr">
         <is>
@@ -5359,7 +5388,7 @@
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>Oil gearbox</t>
+          <t>Cross member threads repair</t>
         </is>
       </c>
       <c r="D180" s="1" t="inlineStr">
@@ -5368,7 +5397,7 @@
         </is>
       </c>
       <c r="E180" s="3" t="n">
-        <v>1524</v>
+        <v>1093</v>
       </c>
       <c r="F180" s="1" t="inlineStr">
         <is>
@@ -5386,16 +5415,16 @@
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>Cross member threads repair</t>
+          <t>Front diff remove &amp; refit</t>
         </is>
       </c>
       <c r="D181" s="1" t="inlineStr">
         <is>
-          <t>Gearbox</t>
+          <t>Diff</t>
         </is>
       </c>
       <c r="E181" s="3" t="n">
-        <v>1093</v>
+        <v>4485</v>
       </c>
       <c r="F181" s="1" t="inlineStr">
         <is>
@@ -5413,7 +5442,7 @@
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>Front diff remove &amp; refit</t>
+          <t>Diff flange</t>
         </is>
       </c>
       <c r="D182" s="1" t="inlineStr">
@@ -5422,7 +5451,7 @@
         </is>
       </c>
       <c r="E182" s="3" t="n">
-        <v>4485</v>
+        <v>2206</v>
       </c>
       <c r="F182" s="1" t="inlineStr">
         <is>
@@ -5440,7 +5469,7 @@
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>Diff flange</t>
+          <t>Solid spacer bearing kit - front diff</t>
         </is>
       </c>
       <c r="D183" s="1" t="inlineStr">
@@ -5449,7 +5478,7 @@
         </is>
       </c>
       <c r="E183" s="3" t="n">
-        <v>2206</v>
+        <v>8280</v>
       </c>
       <c r="F183" s="1" t="inlineStr">
         <is>
@@ -5467,7 +5496,7 @@
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>Solid spacer bearing kit - front diff</t>
+          <t>Wheelbearings front</t>
         </is>
       </c>
       <c r="D184" s="1" t="inlineStr">
@@ -5476,7 +5505,7 @@
         </is>
       </c>
       <c r="E184" s="3" t="n">
-        <v>8280</v>
+        <v>3802</v>
       </c>
       <c r="F184" s="1" t="inlineStr">
         <is>
@@ -5494,7 +5523,7 @@
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>Wheelbearings front</t>
+          <t>CV Joint left outer</t>
         </is>
       </c>
       <c r="D185" s="1" t="inlineStr">
@@ -5503,7 +5532,7 @@
         </is>
       </c>
       <c r="E185" s="3" t="n">
-        <v>3802</v>
+        <v>4725</v>
       </c>
       <c r="F185" s="1" t="inlineStr">
         <is>
@@ -5521,7 +5550,7 @@
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>CV Joint left outer</t>
+          <t>Front Knuckle / Spindle overhaul kit</t>
         </is>
       </c>
       <c r="D186" s="1" t="inlineStr">
@@ -5530,7 +5559,7 @@
         </is>
       </c>
       <c r="E186" s="3" t="n">
-        <v>4725</v>
+        <v>7204</v>
       </c>
       <c r="F186" s="1" t="inlineStr">
         <is>
@@ -5548,7 +5577,7 @@
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>Front Knuckle / Spindle overhaul kit</t>
+          <t>Diff oil - front</t>
         </is>
       </c>
       <c r="D187" s="1" t="inlineStr">
@@ -5557,7 +5586,7 @@
         </is>
       </c>
       <c r="E187" s="3" t="n">
-        <v>7204</v>
+        <v>552</v>
       </c>
       <c r="F187" s="1" t="inlineStr">
         <is>
@@ -5575,7 +5604,7 @@
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>Diff oil - front</t>
+          <t>Rear diff remove &amp; refit</t>
         </is>
       </c>
       <c r="D188" s="1" t="inlineStr">
@@ -5584,7 +5613,7 @@
         </is>
       </c>
       <c r="E188" s="3" t="n">
-        <v>552</v>
+        <v>3738</v>
       </c>
       <c r="F188" s="1" t="inlineStr">
         <is>
@@ -5602,7 +5631,7 @@
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>Rear diff remove &amp; refit</t>
+          <t>Driveshaft rechrome</t>
         </is>
       </c>
       <c r="D189" s="1" t="inlineStr">
@@ -5611,7 +5640,7 @@
         </is>
       </c>
       <c r="E189" s="3" t="n">
-        <v>3738</v>
+        <v>3278</v>
       </c>
       <c r="F189" s="1" t="inlineStr">
         <is>
@@ -5629,7 +5658,7 @@
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>Driveshaft rechrome</t>
+          <t>Solid spacer bearing kit - rear diff</t>
         </is>
       </c>
       <c r="D190" s="1" t="inlineStr">
@@ -5638,7 +5667,7 @@
         </is>
       </c>
       <c r="E190" s="3" t="n">
-        <v>3278</v>
+        <v>8855</v>
       </c>
       <c r="F190" s="1" t="inlineStr">
         <is>
@@ -5656,7 +5685,7 @@
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>Solid spacer bearing kit - rear diff</t>
+          <t>Wheelbearings rear</t>
         </is>
       </c>
       <c r="D191" s="1" t="inlineStr">
@@ -5665,7 +5694,7 @@
         </is>
       </c>
       <c r="E191" s="3" t="n">
-        <v>8855</v>
+        <v>2637</v>
       </c>
       <c r="F191" s="1" t="inlineStr">
         <is>
@@ -5683,7 +5712,7 @@
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>Wheelbearings rear</t>
+          <t>Skim front discs</t>
         </is>
       </c>
       <c r="D192" s="1" t="inlineStr">
@@ -5692,7 +5721,7 @@
         </is>
       </c>
       <c r="E192" s="3" t="n">
-        <v>2637</v>
+        <v>518</v>
       </c>
       <c r="F192" s="1" t="inlineStr">
         <is>
@@ -5710,7 +5739,7 @@
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>Skim front discs</t>
+          <t>Brake pads front</t>
         </is>
       </c>
       <c r="D193" s="1" t="inlineStr">
@@ -5719,7 +5748,7 @@
         </is>
       </c>
       <c r="E193" s="3" t="n">
-        <v>518</v>
+        <v>1851</v>
       </c>
       <c r="F193" s="1" t="inlineStr">
         <is>
@@ -5737,20 +5766,20 @@
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>Brake pads front</t>
+          <t>U-Joint (UJ-230) GUT 21</t>
         </is>
       </c>
       <c r="D194" s="1" t="inlineStr">
         <is>
-          <t>Diff</t>
+          <t>Propshaft</t>
         </is>
       </c>
       <c r="E194" s="3" t="n">
-        <v>1851</v>
+        <v>1190</v>
       </c>
       <c r="F194" s="1" t="inlineStr">
         <is>
-          <t>Cape Transmissions</t>
+          <t>Propshaft Engineering</t>
         </is>
       </c>
       <c r="G194" s="34" t="n"/>
@@ -5764,7 +5793,7 @@
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>U-Joint (UJ-230) GUT 21</t>
+          <t>U-Joint (UJ-234) GUT 20</t>
         </is>
       </c>
       <c r="D195" s="1" t="inlineStr">
@@ -5773,7 +5802,7 @@
         </is>
       </c>
       <c r="E195" s="3" t="n">
-        <v>1190</v>
+        <v>1426</v>
       </c>
       <c r="F195" s="1" t="inlineStr">
         <is>
@@ -5791,7 +5820,7 @@
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>U-Joint (UJ-234) GUT 20</t>
+          <t>Balance single shaft (CAR 2 flange)</t>
         </is>
       </c>
       <c r="D196" s="1" t="inlineStr">
@@ -5800,7 +5829,7 @@
         </is>
       </c>
       <c r="E196" s="3" t="n">
-        <v>1426</v>
+        <v>886</v>
       </c>
       <c r="F196" s="1" t="inlineStr">
         <is>
@@ -5818,7 +5847,7 @@
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>Balance single shaft (CAR 2 flange)</t>
+          <t>Sliding assy  Gut 21</t>
         </is>
       </c>
       <c r="D197" s="1" t="inlineStr">
@@ -5827,7 +5856,7 @@
         </is>
       </c>
       <c r="E197" s="3" t="n">
-        <v>886</v>
+        <v>2012</v>
       </c>
       <c r="F197" s="1" t="inlineStr">
         <is>
@@ -5845,7 +5874,7 @@
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>Sliding assy  Gut 21</t>
+          <t>Sliding assy  Gut 20</t>
         </is>
       </c>
       <c r="D198" s="1" t="inlineStr">
@@ -5861,34 +5890,38 @@
           <t>Propshaft Engineering</t>
         </is>
       </c>
-      <c r="G198" s="34" t="n"/>
+      <c r="G198" s="35" t="n"/>
     </row>
     <row r="199">
       <c r="A199" s="2" t="n">
-        <v>45701</v>
+        <v>45741</v>
       </c>
       <c r="B199" s="27" t="n">
-        <v>271200</v>
+        <v>272185</v>
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>Sliding assy  Gut 20</t>
-        </is>
-      </c>
-      <c r="D199" s="1" t="inlineStr">
-        <is>
-          <t>Propshaft</t>
+          <t>Diesel Pump calibrate</t>
+        </is>
+      </c>
+      <c r="D199" t="inlineStr">
+        <is>
+          <t>Fuel system check</t>
         </is>
       </c>
       <c r="E199" s="3" t="n">
-        <v>2012</v>
-      </c>
-      <c r="F199" s="1" t="inlineStr">
-        <is>
-          <t>Propshaft Engineering</t>
-        </is>
-      </c>
-      <c r="G199" s="35" t="n"/>
+        <v>3163</v>
+      </c>
+      <c r="F199" t="inlineStr">
+        <is>
+          <t>DupDiesel</t>
+        </is>
+      </c>
+      <c r="G199" s="20" t="inlineStr">
+        <is>
+          <t>Dyno: 118kw; 373Nm</t>
+        </is>
+      </c>
     </row>
     <row r="200">
       <c r="A200" s="2" t="n">
@@ -5899,7 +5932,7 @@
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>Diesel Pump calibrate</t>
+          <t>Diesel Pump Timing</t>
         </is>
       </c>
       <c r="D200" t="inlineStr">
@@ -5908,16 +5941,11 @@
         </is>
       </c>
       <c r="E200" s="3" t="n">
-        <v>3163</v>
+        <v>3018</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
           <t>DupDiesel</t>
-        </is>
-      </c>
-      <c r="G200" s="20" t="inlineStr">
-        <is>
-          <t>Dyno: 118kw; 373Nm</t>
         </is>
       </c>
     </row>
@@ -5930,7 +5958,7 @@
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>Diesel Pump Timing</t>
+          <t>Injectors (Reman Toyota )</t>
         </is>
       </c>
       <c r="D201" t="inlineStr">
@@ -5939,7 +5967,7 @@
         </is>
       </c>
       <c r="E201" s="3" t="n">
-        <v>3018</v>
+        <v>7590</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -5956,7 +5984,7 @@
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>Injectors (Reman Toyota )</t>
+          <t>Dyno test</t>
         </is>
       </c>
       <c r="D202" t="inlineStr">
@@ -5965,7 +5993,7 @@
         </is>
       </c>
       <c r="E202" s="3" t="n">
-        <v>7590</v>
+        <v>978</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -5982,7 +6010,7 @@
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>Dyno test</t>
+          <t>Compression test</t>
         </is>
       </c>
       <c r="D203" t="inlineStr">
@@ -5991,7 +6019,7 @@
         </is>
       </c>
       <c r="E203" s="3" t="n">
-        <v>978</v>
+        <v>1438</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -6008,7 +6036,7 @@
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>Compression test</t>
+          <t>Glow plugs test</t>
         </is>
       </c>
       <c r="D204" t="inlineStr">
@@ -6034,7 +6062,7 @@
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t>Glow plugs test</t>
+          <t>Turbo drain hose</t>
         </is>
       </c>
       <c r="D205" t="inlineStr">
@@ -6043,7 +6071,7 @@
         </is>
       </c>
       <c r="E205" s="3" t="n">
-        <v>1438</v>
+        <v>633</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -6053,27 +6081,27 @@
     </row>
     <row r="206">
       <c r="A206" s="2" t="n">
-        <v>45741</v>
+        <v>45770</v>
       </c>
       <c r="B206" s="27" t="n">
-        <v>272185</v>
+        <v>273023</v>
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t>Turbo drain hose</t>
+          <t>Service 275,000 km</t>
         </is>
       </c>
       <c r="D206" t="inlineStr">
         <is>
-          <t>Fuel system check</t>
+          <t>Manufacturers service 275,000 km</t>
         </is>
       </c>
       <c r="E206" s="3" t="n">
-        <v>633</v>
+        <v>19080</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
-          <t>DupDiesel</t>
+          <t>PW Auto Centre</t>
         </is>
       </c>
     </row>
@@ -6086,7 +6114,7 @@
       </c>
       <c r="C207" t="inlineStr">
         <is>
-          <t>Service 275,000 km</t>
+          <t>Filter kit</t>
         </is>
       </c>
       <c r="D207" t="inlineStr">
@@ -6095,7 +6123,7 @@
         </is>
       </c>
       <c r="E207" s="3" t="n">
-        <v>19080</v>
+        <v>3337</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -6112,7 +6140,7 @@
       </c>
       <c r="C208" t="inlineStr">
         <is>
-          <t>Filter kit</t>
+          <t>Grease propshaft</t>
         </is>
       </c>
       <c r="D208" t="inlineStr">
@@ -6121,7 +6149,7 @@
         </is>
       </c>
       <c r="E208" s="3" t="n">
-        <v>3337</v>
+        <v>77</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -6138,7 +6166,7 @@
       </c>
       <c r="C209" t="inlineStr">
         <is>
-          <t>Grease propshaft</t>
+          <t>Greas steering</t>
         </is>
       </c>
       <c r="D209" t="inlineStr">
@@ -6164,7 +6192,7 @@
       </c>
       <c r="C210" t="inlineStr">
         <is>
-          <t>Greas steering</t>
+          <t>Grease suspension</t>
         </is>
       </c>
       <c r="D210" t="inlineStr">
@@ -6190,7 +6218,7 @@
       </c>
       <c r="C211" t="inlineStr">
         <is>
-          <t>Grease suspension</t>
+          <t>Diff oil</t>
         </is>
       </c>
       <c r="D211" t="inlineStr">
@@ -6199,7 +6227,7 @@
         </is>
       </c>
       <c r="E211" s="3" t="n">
-        <v>77</v>
+        <v>184</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -6216,16 +6244,16 @@
       </c>
       <c r="C212" t="inlineStr">
         <is>
-          <t>Diff oil</t>
+          <t>Engine cover</t>
         </is>
       </c>
       <c r="D212" t="inlineStr">
         <is>
-          <t>Manufacturers service 275,000 km</t>
+          <t>Engine cover</t>
         </is>
       </c>
       <c r="E212" s="3" t="n">
-        <v>184</v>
+        <v>2600</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -6242,16 +6270,16 @@
       </c>
       <c r="C213" t="inlineStr">
         <is>
-          <t>Engine cover</t>
+          <t>Radiator cap</t>
         </is>
       </c>
       <c r="D213" t="inlineStr">
         <is>
-          <t>Engine cover</t>
+          <t>Radiator</t>
         </is>
       </c>
       <c r="E213" s="3" t="n">
-        <v>2600</v>
+        <v>493</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -6268,16 +6296,16 @@
       </c>
       <c r="C214" t="inlineStr">
         <is>
-          <t>Radiator cap</t>
+          <t>Fan belt kit</t>
         </is>
       </c>
       <c r="D214" t="inlineStr">
         <is>
-          <t>Radiator</t>
+          <t>Fan belt</t>
         </is>
       </c>
       <c r="E214" s="3" t="n">
-        <v>493</v>
+        <v>1700</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -6294,16 +6322,16 @@
       </c>
       <c r="C215" t="inlineStr">
         <is>
-          <t>Fan belt kit</t>
+          <t>Front stabiliser bush kit</t>
         </is>
       </c>
       <c r="D215" t="inlineStr">
         <is>
-          <t>Fan belt</t>
+          <t>Manufacturers service 275,000 km</t>
         </is>
       </c>
       <c r="E215" s="3" t="n">
-        <v>1700</v>
+        <v>1000</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -6320,20 +6348,25 @@
       </c>
       <c r="C216" t="inlineStr">
         <is>
-          <t>Front stabiliser bush kit</t>
+          <t>Cambelt</t>
         </is>
       </c>
       <c r="D216" t="inlineStr">
         <is>
-          <t>Manufacturers service 275,000 km</t>
+          <t>Cambelt</t>
         </is>
       </c>
       <c r="E216" s="3" t="n">
-        <v>1000</v>
+        <v>1812</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
           <t>PW Auto Centre</t>
+        </is>
+      </c>
+      <c r="G216" s="18" t="inlineStr">
+        <is>
+          <t>Cambelt change 273,000km</t>
         </is>
       </c>
     </row>
@@ -6346,25 +6379,20 @@
       </c>
       <c r="C217" t="inlineStr">
         <is>
+          <t>Cambelt Tensioner</t>
+        </is>
+      </c>
+      <c r="D217" t="inlineStr">
+        <is>
           <t>Cambelt</t>
         </is>
       </c>
-      <c r="D217" t="inlineStr">
-        <is>
-          <t>Cambelt</t>
-        </is>
-      </c>
       <c r="E217" s="3" t="n">
-        <v>1812</v>
+        <v>1750</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
           <t>PW Auto Centre</t>
-        </is>
-      </c>
-      <c r="G217" s="18" t="inlineStr">
-        <is>
-          <t>Cambelt change 273,000km</t>
         </is>
       </c>
     </row>
@@ -6377,7 +6405,7 @@
       </c>
       <c r="C218" t="inlineStr">
         <is>
-          <t>Cambelt Tensioner</t>
+          <t>Cambelt Idler</t>
         </is>
       </c>
       <c r="D218" t="inlineStr">
@@ -6386,7 +6414,7 @@
         </is>
       </c>
       <c r="E218" s="3" t="n">
-        <v>1750</v>
+        <v>3361</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -6403,7 +6431,7 @@
       </c>
       <c r="C219" t="inlineStr">
         <is>
-          <t>Cambelt Idler</t>
+          <t>Cambelt Cover</t>
         </is>
       </c>
       <c r="D219" t="inlineStr">
@@ -6412,7 +6440,7 @@
         </is>
       </c>
       <c r="E219" s="3" t="n">
-        <v>3361</v>
+        <v>1250</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -6429,7 +6457,7 @@
       </c>
       <c r="C220" t="inlineStr">
         <is>
-          <t>Cambelt Cover</t>
+          <t>Cambelt Cover gasket</t>
         </is>
       </c>
       <c r="D220" t="inlineStr">
@@ -6438,7 +6466,7 @@
         </is>
       </c>
       <c r="E220" s="3" t="n">
-        <v>1250</v>
+        <v>247</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -6455,7 +6483,7 @@
       </c>
       <c r="C221" t="inlineStr">
         <is>
-          <t>Cambelt Cover gasket</t>
+          <t>Cambelt washer bolts</t>
         </is>
       </c>
       <c r="D221" t="inlineStr">
@@ -6464,7 +6492,7 @@
         </is>
       </c>
       <c r="E221" s="3" t="n">
-        <v>247</v>
+        <v>343</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -6481,16 +6509,16 @@
       </c>
       <c r="C222" t="inlineStr">
         <is>
-          <t>Cambelt washer bolts</t>
+          <t>Brake fluid</t>
         </is>
       </c>
       <c r="D222" t="inlineStr">
         <is>
-          <t>Cambelt</t>
+          <t>Manufacturers service 275,000 km</t>
         </is>
       </c>
       <c r="E222" s="3" t="n">
-        <v>343</v>
+        <v>104</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -6507,7 +6535,7 @@
       </c>
       <c r="C223" t="inlineStr">
         <is>
-          <t>Brake fluid</t>
+          <t>Clutch fluid</t>
         </is>
       </c>
       <c r="D223" t="inlineStr">
@@ -6533,16 +6561,16 @@
       </c>
       <c r="C224" t="inlineStr">
         <is>
-          <t>Clutch fluid</t>
+          <t>Coolant</t>
         </is>
       </c>
       <c r="D224" t="inlineStr">
         <is>
-          <t>Manufacturers service 275,000 km</t>
+          <t>Cooling system</t>
         </is>
       </c>
       <c r="E224" s="3" t="n">
-        <v>104</v>
+        <v>575</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -6559,16 +6587,16 @@
       </c>
       <c r="C225" t="inlineStr">
         <is>
-          <t>Coolant</t>
+          <t>Engin oil</t>
         </is>
       </c>
       <c r="D225" t="inlineStr">
         <is>
-          <t>Cooling system</t>
+          <t>Manufacturers service 275,000 km</t>
         </is>
       </c>
       <c r="E225" s="3" t="n">
-        <v>575</v>
+        <v>1472</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -6585,20 +6613,20 @@
       </c>
       <c r="C226" t="inlineStr">
         <is>
-          <t>Engin oil</t>
+          <t>Rear bushes kit polyurethane</t>
         </is>
       </c>
       <c r="D226" t="inlineStr">
         <is>
-          <t>Manufacturers service 275,000 km</t>
+          <t>Bushes</t>
         </is>
       </c>
       <c r="E226" s="3" t="n">
-        <v>1472</v>
+        <v>3106</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
-          <t>PW Auto Centre</t>
+          <t>First Alignment</t>
         </is>
       </c>
     </row>
@@ -6611,16 +6639,16 @@
       </c>
       <c r="C227" t="inlineStr">
         <is>
-          <t>Rear bushes kit polyurethane</t>
+          <t>Castor correction</t>
         </is>
       </c>
       <c r="D227" t="inlineStr">
         <is>
-          <t>Bushes</t>
+          <t>Suspension</t>
         </is>
       </c>
       <c r="E227" s="3" t="n">
-        <v>3106</v>
+        <v>0</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -6630,14 +6658,14 @@
     </row>
     <row r="228">
       <c r="A228" s="2" t="n">
-        <v>45770</v>
+        <v>45826</v>
       </c>
       <c r="B228" s="27" t="n">
-        <v>273023</v>
+        <v>275000</v>
       </c>
       <c r="C228" t="inlineStr">
         <is>
-          <t>Castor correction</t>
+          <t>Plate &amp; weld trailing arm support bracket on front diff</t>
         </is>
       </c>
       <c r="D228" t="inlineStr">
@@ -6646,175 +6674,175 @@
         </is>
       </c>
       <c r="E228" s="3" t="n">
-        <v>0</v>
+        <v>4006</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
-          <t>First Alignment</t>
+          <t>Suspension City</t>
+        </is>
+      </c>
+      <c r="G228" s="32" t="inlineStr">
+        <is>
+          <t>Corrected castor correction as the LC was pulling to the left a lot</t>
         </is>
       </c>
     </row>
     <row r="229">
       <c r="A229" s="2" t="n">
-        <v>45782</v>
+        <v>45882</v>
       </c>
       <c r="B229" s="27" t="n">
-        <v>274000</v>
+        <v>278675</v>
       </c>
       <c r="C229" t="inlineStr">
         <is>
-          <t>TPMS (TP-V31) Solar Powered Internal)</t>
+          <t>Sideshaft oil seal replace (left front side)</t>
         </is>
       </c>
       <c r="D229" t="inlineStr">
         <is>
-          <t>TPMS</t>
+          <t>Left front sideshaft oil seal</t>
         </is>
       </c>
       <c r="E229" s="3" t="n">
-        <v>3450</v>
+        <v>5514</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
-          <t>First Alignment</t>
+          <t>Northam Toyota</t>
         </is>
       </c>
     </row>
     <row r="230">
       <c r="A230" s="2" t="n">
-        <v>45826</v>
+        <v>45882</v>
       </c>
       <c r="B230" s="27" t="n">
-        <v>275000</v>
+        <v>278675</v>
       </c>
       <c r="C230" t="inlineStr">
         <is>
-          <t>Plate &amp; weld trailing arm support bracket on front diff</t>
+          <t>Gasket (knucle, front axle)</t>
         </is>
       </c>
       <c r="D230" t="inlineStr">
         <is>
-          <t>Suspension</t>
+          <t>Left front sideshaft oil seal</t>
         </is>
       </c>
       <c r="E230" s="3" t="n">
-        <v>4006</v>
+        <v>100</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
-          <t>Suspension City</t>
-        </is>
-      </c>
-      <c r="G230" s="32" t="inlineStr">
-        <is>
-          <t>Corrected castor correction as the LC was pulling to the left a lot</t>
+          <t>Northam Toyota</t>
         </is>
       </c>
     </row>
     <row r="231">
       <c r="A231" s="2" t="n">
-        <v>45882</v>
+        <v>45911</v>
       </c>
       <c r="B231" s="27" t="n">
-        <v>278675</v>
+        <v>281671</v>
       </c>
       <c r="C231" t="inlineStr">
         <is>
-          <t>Sideshaft oil seal replace (left front side)</t>
+          <t xml:space="preserve">Service 280,000 </t>
         </is>
       </c>
       <c r="D231" t="inlineStr">
         <is>
-          <t>Left front sideshaft oil seal</t>
+          <t>Manufacturers service 280,000 km</t>
         </is>
       </c>
       <c r="E231" s="3" t="n">
-        <v>5514</v>
+        <v>6840</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
-          <t>Northam Toyota</t>
+          <t>Croco Toyota Mutare</t>
         </is>
       </c>
     </row>
     <row r="232">
-      <c r="A232" s="2" t="n">
-        <v>45882</v>
-      </c>
-      <c r="B232" s="27" t="n">
-        <v>278675</v>
-      </c>
-      <c r="C232" t="inlineStr">
-        <is>
-          <t>Gasket (knucle, front axle)</t>
-        </is>
-      </c>
-      <c r="D232" t="inlineStr">
-        <is>
-          <t>Left front sideshaft oil seal</t>
-        </is>
-      </c>
-      <c r="E232" s="3" t="n">
-        <v>100</v>
-      </c>
-      <c r="F232" t="inlineStr">
-        <is>
-          <t>Northam Toyota</t>
+      <c r="A232" s="13" t="n">
+        <v>46023</v>
+      </c>
+      <c r="B232" s="30" t="n">
+        <v>293444</v>
+      </c>
+      <c r="C232" s="38" t="inlineStr">
+        <is>
+          <t>Year end</t>
+        </is>
+      </c>
+      <c r="D232" s="38" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="E232" s="14" t="n"/>
+      <c r="F232" s="38" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="G232" s="32" t="inlineStr">
+        <is>
+          <t>30,000km on Tyres now</t>
         </is>
       </c>
     </row>
     <row r="233">
       <c r="A233" s="2" t="n">
-        <v>45911</v>
+        <v>46041</v>
       </c>
       <c r="B233" s="27" t="n">
-        <v>281671</v>
+        <v>293949</v>
       </c>
       <c r="C233" t="inlineStr">
         <is>
-          <t xml:space="preserve">Service 280,000 </t>
+          <t>Service 295,000 km</t>
         </is>
       </c>
       <c r="D233" t="inlineStr">
         <is>
-          <t>Manufacturers service 280,000 km</t>
+          <t>Manufacturers service 295,000 km</t>
         </is>
       </c>
       <c r="E233" s="3" t="n">
-        <v>6840</v>
+        <v>16227</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
-          <t>Croco Toyota Mutare</t>
+          <t>PW Auto Centre</t>
         </is>
       </c>
     </row>
     <row r="234">
-      <c r="A234" s="13" t="n">
-        <v>46023</v>
-      </c>
-      <c r="B234" s="30" t="n">
-        <v>293444</v>
-      </c>
-      <c r="C234" s="12" t="inlineStr">
-        <is>
-          <t>Year end</t>
-        </is>
-      </c>
-      <c r="D234" s="12" t="inlineStr">
-        <is>
-          <t>n/a</t>
-        </is>
-      </c>
-      <c r="E234" s="14" t="n"/>
-      <c r="F234" s="12" t="inlineStr">
-        <is>
-          <t>n/a</t>
-        </is>
-      </c>
-      <c r="G234" s="32" t="inlineStr">
-        <is>
-          <t>30,000km on Tyres now</t>
+      <c r="A234" s="2" t="n">
+        <v>46041</v>
+      </c>
+      <c r="B234" s="27" t="n">
+        <v>293949</v>
+      </c>
+      <c r="C234" t="inlineStr">
+        <is>
+          <t>Grease propshaft</t>
+        </is>
+      </c>
+      <c r="D234" t="inlineStr">
+        <is>
+          <t>Manufacturers service 295,000 km</t>
+        </is>
+      </c>
+      <c r="E234" s="3" t="n">
+        <v>77</v>
+      </c>
+      <c r="F234" t="inlineStr">
+        <is>
+          <t>PW Auto Centre</t>
         </is>
       </c>
     </row>
@@ -6827,7 +6855,7 @@
       </c>
       <c r="C235" t="inlineStr">
         <is>
-          <t>Service 295,000 km</t>
+          <t>Grease steering</t>
         </is>
       </c>
       <c r="D235" t="inlineStr">
@@ -6836,7 +6864,7 @@
         </is>
       </c>
       <c r="E235" s="3" t="n">
-        <v>16227</v>
+        <v>77</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -6853,7 +6881,7 @@
       </c>
       <c r="C236" t="inlineStr">
         <is>
-          <t>Grease propshaft</t>
+          <t>Grease suspension</t>
         </is>
       </c>
       <c r="D236" t="inlineStr">
@@ -6861,7 +6889,7 @@
           <t>Manufacturers service 295,000 km</t>
         </is>
       </c>
-      <c r="E236" s="17" t="n">
+      <c r="E236" s="3" t="n">
         <v>77</v>
       </c>
       <c r="F236" t="inlineStr">
@@ -6879,7 +6907,7 @@
       </c>
       <c r="C237" t="inlineStr">
         <is>
-          <t>Grease steering</t>
+          <t>Grease nipples</t>
         </is>
       </c>
       <c r="D237" t="inlineStr">
@@ -6887,8 +6915,8 @@
           <t>Manufacturers service 295,000 km</t>
         </is>
       </c>
-      <c r="E237" s="17" t="n">
-        <v>77</v>
+      <c r="E237" s="3" t="n">
+        <v>80</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -6905,7 +6933,7 @@
       </c>
       <c r="C238" t="inlineStr">
         <is>
-          <t>Grease suspension</t>
+          <t>Axle gasket L.Front</t>
         </is>
       </c>
       <c r="D238" t="inlineStr">
@@ -6913,8 +6941,8 @@
           <t>Manufacturers service 295,000 km</t>
         </is>
       </c>
-      <c r="E238" s="17" t="n">
-        <v>77</v>
+      <c r="E238" s="3" t="n">
+        <v>69</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -6931,7 +6959,7 @@
       </c>
       <c r="C239" t="inlineStr">
         <is>
-          <t>Grease nipples</t>
+          <t>Diff oil - front</t>
         </is>
       </c>
       <c r="D239" t="inlineStr">
@@ -6939,8 +6967,8 @@
           <t>Manufacturers service 295,000 km</t>
         </is>
       </c>
-      <c r="E239" s="17" t="n">
-        <v>80</v>
+      <c r="E239" s="3" t="n">
+        <v>897</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -6950,23 +6978,23 @@
     </row>
     <row r="240">
       <c r="A240" s="2" t="n">
-        <v>46041</v>
+        <v>46042</v>
       </c>
       <c r="B240" s="27" t="n">
         <v>293949</v>
       </c>
       <c r="C240" t="inlineStr">
         <is>
-          <t>Axle gasket L.Front</t>
+          <t>Air con pulley</t>
         </is>
       </c>
       <c r="D240" t="inlineStr">
         <is>
-          <t>Manufacturers service 295,000 km</t>
+          <t>Aircon pulley</t>
         </is>
       </c>
       <c r="E240" s="3" t="n">
-        <v>69</v>
+        <v>5400</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -6976,23 +7004,23 @@
     </row>
     <row r="241">
       <c r="A241" s="2" t="n">
-        <v>46041</v>
+        <v>46043</v>
       </c>
       <c r="B241" s="27" t="n">
         <v>293949</v>
       </c>
       <c r="C241" t="inlineStr">
         <is>
-          <t>Diff oil - front</t>
+          <t>Rear brake shoes</t>
         </is>
       </c>
       <c r="D241" t="inlineStr">
         <is>
-          <t>Manufacturers service 295,000 km</t>
+          <t>Brakes</t>
         </is>
       </c>
       <c r="E241" s="3" t="n">
-        <v>897</v>
+        <v>2868</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -7002,23 +7030,23 @@
     </row>
     <row r="242">
       <c r="A242" s="2" t="n">
-        <v>46042</v>
+        <v>46044</v>
       </c>
       <c r="B242" s="27" t="n">
         <v>293949</v>
       </c>
       <c r="C242" t="inlineStr">
         <is>
-          <t>Air con pulley</t>
+          <t>Rear brake drum X  2</t>
         </is>
       </c>
       <c r="D242" t="inlineStr">
         <is>
-          <t>Aircon pulley</t>
+          <t>Brakes</t>
         </is>
       </c>
       <c r="E242" s="3" t="n">
-        <v>5400</v>
+        <v>10911</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -7028,23 +7056,23 @@
     </row>
     <row r="243">
       <c r="A243" s="2" t="n">
-        <v>46043</v>
+        <v>46045</v>
       </c>
       <c r="B243" s="27" t="n">
         <v>293949</v>
       </c>
       <c r="C243" t="inlineStr">
         <is>
-          <t>Rear brake shoes</t>
+          <t>Fan belt kit</t>
         </is>
       </c>
       <c r="D243" t="inlineStr">
         <is>
-          <t>Brakes</t>
+          <t>Fan belt</t>
         </is>
       </c>
       <c r="E243" s="3" t="n">
-        <v>2868</v>
+        <v>1950</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -7054,23 +7082,23 @@
     </row>
     <row r="244">
       <c r="A244" s="2" t="n">
-        <v>46044</v>
+        <v>46045</v>
       </c>
       <c r="B244" s="27" t="n">
         <v>293949</v>
       </c>
       <c r="C244" t="inlineStr">
         <is>
-          <t>Rear brake drum X  2</t>
+          <t>Coolant</t>
         </is>
       </c>
       <c r="D244" t="inlineStr">
         <is>
-          <t>Brakes</t>
+          <t>Cooling system</t>
         </is>
       </c>
       <c r="E244" s="3" t="n">
-        <v>10911</v>
+        <v>207</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -7087,16 +7115,16 @@
       </c>
       <c r="C245" t="inlineStr">
         <is>
-          <t>Fan belt kit</t>
+          <t>Filter kit</t>
         </is>
       </c>
       <c r="D245" t="inlineStr">
         <is>
-          <t>Fan belt</t>
+          <t>Manufacturers service 295,000 km</t>
         </is>
       </c>
       <c r="E245" s="3" t="n">
-        <v>1950</v>
+        <v>2820</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -7113,16 +7141,16 @@
       </c>
       <c r="C246" t="inlineStr">
         <is>
-          <t>Coolant</t>
+          <t>Engin oil</t>
         </is>
       </c>
       <c r="D246" t="inlineStr">
         <is>
-          <t>Cooling system</t>
+          <t>Manufacturers service 295,000 km</t>
         </is>
       </c>
       <c r="E246" s="3" t="n">
-        <v>207</v>
+        <v>1500</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -7139,7 +7167,7 @@
       </c>
       <c r="C247" t="inlineStr">
         <is>
-          <t>Filter kit</t>
+          <t>Brake fluid</t>
         </is>
       </c>
       <c r="D247" t="inlineStr">
@@ -7148,7 +7176,7 @@
         </is>
       </c>
       <c r="E247" s="3" t="n">
-        <v>2820</v>
+        <v>125</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -7158,141 +7186,137 @@
     </row>
     <row r="248">
       <c r="A248" s="2" t="n">
-        <v>46045</v>
+        <v>46050</v>
       </c>
       <c r="B248" s="27" t="n">
-        <v>293949</v>
+        <v>294500</v>
       </c>
       <c r="C248" t="inlineStr">
         <is>
-          <t>Engin oil</t>
+          <t>Leaf Springs OME (CS058R)</t>
         </is>
       </c>
       <c r="D248" t="inlineStr">
         <is>
-          <t>Manufacturers service 295,000 km</t>
+          <t>Suspension</t>
         </is>
       </c>
       <c r="E248" s="3" t="n">
-        <v>1500</v>
+        <v>24142</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
-          <t>PW Auto Centre</t>
+          <t>4X4 Megaworld</t>
+        </is>
+      </c>
+      <c r="G248" s="32" t="inlineStr">
+        <is>
+          <t>Repllace broken Leaf Spring - Fit new set including shocks</t>
         </is>
       </c>
     </row>
     <row r="249">
       <c r="A249" s="2" t="n">
-        <v>46045</v>
+        <v>46050</v>
       </c>
       <c r="B249" s="27" t="n">
-        <v>293949</v>
+        <v>294500</v>
       </c>
       <c r="C249" t="inlineStr">
         <is>
-          <t>Brake fluid</t>
+          <t>Shocks Rear (OME - Nitrocharger Plus 63111)</t>
         </is>
       </c>
       <c r="D249" t="inlineStr">
         <is>
-          <t>Manufacturers service 295,000 km</t>
+          <t>Suspension</t>
         </is>
       </c>
       <c r="E249" s="3" t="n">
-        <v>125</v>
+        <v>8620</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
-          <t>PW Auto Centre</t>
+          <t>4X4 Megaworld</t>
         </is>
       </c>
     </row>
     <row r="250">
       <c r="A250" s="2" t="n">
-        <v>46043</v>
+        <v>46050</v>
       </c>
       <c r="B250" s="27" t="n">
-        <v>294000</v>
-      </c>
-      <c r="C250" t="inlineStr">
-        <is>
-          <t>Isolator Victron Cyrix 120A</t>
+        <v>294500</v>
+      </c>
+      <c r="C250" s="15" t="inlineStr">
+        <is>
+          <t>Spring Bushes (Greasable Shackle)</t>
         </is>
       </c>
       <c r="D250" t="inlineStr">
         <is>
-          <t>Battery</t>
+          <t>Suspension</t>
         </is>
       </c>
       <c r="E250" s="3" t="n">
-        <v>1140</v>
+        <v>2268</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
-          <t>HBC Systems</t>
-        </is>
-      </c>
-      <c r="G250" s="32" t="inlineStr">
-        <is>
-          <t>Jos Hartog and Wayne</t>
-        </is>
-      </c>
+          <t>4X4 Megaworld</t>
+        </is>
+      </c>
+      <c r="G250" s="37" t="n"/>
     </row>
     <row r="251">
       <c r="A251" s="2" t="n">
-        <v>46043</v>
+        <v>46050</v>
       </c>
       <c r="B251" s="27" t="n">
-        <v>294000</v>
-      </c>
-      <c r="C251" t="inlineStr">
-        <is>
-          <t>BM 2000 Dual Battery Monitor</t>
+        <v>294500</v>
+      </c>
+      <c r="C251" s="1" t="inlineStr">
+        <is>
+          <t>Stone Guard Kit</t>
         </is>
       </c>
       <c r="D251" t="inlineStr">
         <is>
-          <t>Battery</t>
+          <t>Suspension</t>
         </is>
       </c>
       <c r="E251" s="3" t="n">
-        <v>684</v>
+        <v>625</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
-          <t>HBC Systems</t>
-        </is>
-      </c>
-      <c r="G251" s="32" t="inlineStr">
-        <is>
-          <t>Change National Luna monitor that was drawing lots of power</t>
+          <t>4X4 Megaworld</t>
         </is>
       </c>
     </row>
     <row r="252">
       <c r="A252" s="2" t="n">
-        <v>46043</v>
+        <v>46050</v>
       </c>
       <c r="B252" s="27" t="n">
-        <v>294000</v>
-      </c>
-      <c r="C252" t="inlineStr">
-        <is>
-          <t>Labour</t>
+        <v>294500</v>
+      </c>
+      <c r="C252" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">U Bolt </t>
         </is>
       </c>
       <c r="D252" t="inlineStr">
         <is>
-          <t>Battery</t>
+          <t>Suspension</t>
         </is>
       </c>
       <c r="E252" s="3" t="n">
-        <v>597</v>
+        <v>1848</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
-          <t>HBC Systems</t>
+          <t>4X4 Megaworld</t>
         </is>
       </c>
     </row>
@@ -7305,7 +7329,7 @@
       </c>
       <c r="C253" t="inlineStr">
         <is>
-          <t>Leaf Springs OME (CS058R)</t>
+          <t>Labour</t>
         </is>
       </c>
       <c r="D253" t="inlineStr">
@@ -7314,16 +7338,11 @@
         </is>
       </c>
       <c r="E253" s="3" t="n">
-        <v>24142</v>
+        <v>1400</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
           <t>4X4 Megaworld</t>
-        </is>
-      </c>
-      <c r="G253" s="32" t="inlineStr">
-        <is>
-          <t>Repllace broken Leaf Spring - Fit new set including shocks</t>
         </is>
       </c>
     </row>
@@ -7334,88 +7353,102 @@
       <c r="B254" s="27" t="n">
         <v>294500</v>
       </c>
-      <c r="C254" t="inlineStr">
-        <is>
-          <t>Shocks Rear (OME - Nitrocharger Plus 63111)</t>
+      <c r="C254" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Wheel alignment </t>
         </is>
       </c>
       <c r="D254" t="inlineStr">
         <is>
-          <t>Suspension</t>
+          <t>Wheel alignment</t>
         </is>
       </c>
       <c r="E254" s="3" t="n">
-        <v>8620</v>
+        <v>725</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
-          <t>4X4 Megaworld</t>
-        </is>
-      </c>
-    </row>
-    <row r="255" ht="15" customHeight="1">
+          <t>Hi-Q</t>
+        </is>
+      </c>
+      <c r="G254" s="32" t="inlineStr">
+        <is>
+          <t>Hi-Q Paarden Eiland. Technician - Jerome</t>
+        </is>
+      </c>
+    </row>
+    <row r="255">
       <c r="A255" s="2" t="n">
-        <v>46050</v>
+        <v>46078</v>
       </c>
       <c r="B255" s="27" t="n">
-        <v>294500</v>
-      </c>
-      <c r="C255" s="15" t="inlineStr">
-        <is>
-          <t>Spring Bushes (Greasable Shackle)</t>
+        <v>296500</v>
+      </c>
+      <c r="C255" t="inlineStr">
+        <is>
+          <t>Clutch kit (heavy duty) (TT)</t>
         </is>
       </c>
       <c r="D255" t="inlineStr">
         <is>
-          <t>Suspension</t>
+          <t>Clutch</t>
         </is>
       </c>
       <c r="E255" s="3" t="n">
-        <v>2268</v>
+        <v>21239</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
-          <t>4X4 Megaworld</t>
-        </is>
-      </c>
-      <c r="G255" s="37" t="n"/>
+          <t>Cape Transmissions</t>
+        </is>
+      </c>
+      <c r="G255" s="8" t="inlineStr">
+        <is>
+          <t>Stiff 1st gear and change from 5th to 4th, as well as reverse. Terain Tamer kit</t>
+        </is>
+      </c>
     </row>
     <row r="256">
       <c r="A256" s="2" t="n">
-        <v>46050</v>
+        <v>46086</v>
       </c>
       <c r="B256" s="27" t="n">
-        <v>294500</v>
-      </c>
-      <c r="C256" s="1" t="inlineStr">
-        <is>
-          <t>Stone Guard Kit</t>
+        <v>296600</v>
+      </c>
+      <c r="C256" t="inlineStr">
+        <is>
+          <t>Exhaust mounting  - rear</t>
         </is>
       </c>
       <c r="D256" t="inlineStr">
         <is>
-          <t>Suspension</t>
+          <t>Exhaust</t>
         </is>
       </c>
       <c r="E256" s="3" t="n">
-        <v>625</v>
+        <v>750</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
-          <t>4X4 Megaworld</t>
+          <t xml:space="preserve">Powerflow Exhausts </t>
+        </is>
+      </c>
+      <c r="G256" s="32" t="inlineStr">
+        <is>
+          <t>Also have extra one as a spare</t>
         </is>
       </c>
     </row>
     <row r="257">
       <c r="A257" s="2" t="n">
-        <v>46050</v>
+        <v>46086</v>
       </c>
       <c r="B257" s="27" t="n">
-        <v>294500</v>
-      </c>
-      <c r="C257" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">U Bolt </t>
+        <v>296000</v>
+      </c>
+      <c r="C257" t="inlineStr">
+        <is>
+          <t>Shackle bushes - regrease</t>
         </is>
       </c>
       <c r="D257" t="inlineStr">
@@ -7424,161 +7457,146 @@
         </is>
       </c>
       <c r="E257" s="3" t="n">
-        <v>1848</v>
+        <v>598</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
-          <t>4X4 Megaworld</t>
+          <t>Suspension City</t>
+        </is>
+      </c>
+      <c r="G257" s="32" t="inlineStr">
+        <is>
+          <t>Sqeaking noise from suspension</t>
         </is>
       </c>
     </row>
     <row r="258">
       <c r="A258" s="2" t="n">
-        <v>46050</v>
+        <v>46126</v>
       </c>
       <c r="B258" s="27" t="n">
-        <v>294500</v>
-      </c>
-      <c r="C258" t="inlineStr">
-        <is>
-          <t>Labour</t>
-        </is>
-      </c>
-      <c r="D258" t="inlineStr">
-        <is>
-          <t>Suspension</t>
+        <v>308248</v>
+      </c>
+      <c r="C258" s="1" t="inlineStr">
+        <is>
+          <t>Engin oil</t>
+        </is>
+      </c>
+      <c r="D258" s="1" t="inlineStr">
+        <is>
+          <t>Manufacturers service 310,000 km</t>
         </is>
       </c>
       <c r="E258" s="3" t="n">
-        <v>1400</v>
-      </c>
-      <c r="F258" t="inlineStr">
-        <is>
-          <t>4X4 Megaworld</t>
+        <v>1495</v>
+      </c>
+      <c r="F258" s="1" t="inlineStr">
+        <is>
+          <t>PW Auto Centre</t>
         </is>
       </c>
     </row>
     <row r="259">
       <c r="A259" s="2" t="n">
-        <v>46050</v>
+        <v>46126</v>
       </c>
       <c r="B259" s="27" t="n">
-        <v>294500</v>
-      </c>
-      <c r="C259" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Wheel alignment </t>
-        </is>
-      </c>
-      <c r="D259" t="inlineStr">
-        <is>
-          <t>Wheel alignment</t>
+        <v>308248</v>
+      </c>
+      <c r="C259" t="inlineStr">
+        <is>
+          <t>O-rings</t>
+        </is>
+      </c>
+      <c r="D259" s="1" t="inlineStr">
+        <is>
+          <t>Manufacturers service 310,000 km</t>
         </is>
       </c>
       <c r="E259" s="3" t="n">
-        <v>725</v>
-      </c>
-      <c r="F259" t="inlineStr">
-        <is>
-          <t>Hi-Q</t>
-        </is>
-      </c>
-      <c r="G259" s="32" t="inlineStr">
-        <is>
-          <t>Hi-Q Paarden Eiland. Technician - Jerome</t>
+        <v>155</v>
+      </c>
+      <c r="F259" s="1" t="inlineStr">
+        <is>
+          <t>PW Auto Centre</t>
         </is>
       </c>
     </row>
     <row r="260">
       <c r="A260" s="2" t="n">
-        <v>46078</v>
+        <v>46126</v>
       </c>
       <c r="B260" s="27" t="n">
-        <v>296500</v>
+        <v>308248</v>
       </c>
       <c r="C260" t="inlineStr">
         <is>
-          <t>Clutch kit (heavy duty) (TT)</t>
-        </is>
-      </c>
-      <c r="D260" t="inlineStr">
-        <is>
-          <t>Clutch</t>
+          <t>Brake fluid top up</t>
+        </is>
+      </c>
+      <c r="D260" s="1" t="inlineStr">
+        <is>
+          <t>Manufacturers service 310,000 km</t>
         </is>
       </c>
       <c r="E260" s="3" t="n">
-        <v>21239</v>
-      </c>
-      <c r="F260" t="inlineStr">
-        <is>
-          <t>Cape Transmissions</t>
-        </is>
-      </c>
-      <c r="G260" s="8" t="inlineStr">
-        <is>
-          <t>Stiff 1st gear and change from 5th to 4th, as well as reverse. Terain Tamer kit</t>
+        <v>40</v>
+      </c>
+      <c r="F260" s="1" t="inlineStr">
+        <is>
+          <t>PW Auto Centre</t>
         </is>
       </c>
     </row>
     <row r="261">
       <c r="A261" s="2" t="n">
-        <v>46086</v>
+        <v>46126</v>
       </c>
       <c r="B261" s="27" t="n">
-        <v>296600</v>
+        <v>308248</v>
       </c>
       <c r="C261" t="inlineStr">
         <is>
-          <t>Exhaust mounting  - rear</t>
-        </is>
-      </c>
-      <c r="D261" t="inlineStr">
-        <is>
-          <t>Exhaust</t>
+          <t>Coolant top up</t>
+        </is>
+      </c>
+      <c r="D261" s="1" t="inlineStr">
+        <is>
+          <t>Cooling system</t>
         </is>
       </c>
       <c r="E261" s="3" t="n">
-        <v>750</v>
-      </c>
-      <c r="F261" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Powerflow Exhausts </t>
-        </is>
-      </c>
-      <c r="G261" s="32" t="inlineStr">
-        <is>
-          <t>Also have extra one as a spare</t>
+        <v>322</v>
+      </c>
+      <c r="F261" s="1" t="inlineStr">
+        <is>
+          <t>PW Auto Centre</t>
         </is>
       </c>
     </row>
     <row r="262">
       <c r="A262" s="2" t="n">
-        <v>46086</v>
+        <v>46126</v>
       </c>
       <c r="B262" s="27" t="n">
-        <v>296000</v>
+        <v>308248</v>
       </c>
       <c r="C262" t="inlineStr">
         <is>
-          <t>Shackle bushes - regrease</t>
-        </is>
-      </c>
-      <c r="D262" t="inlineStr">
-        <is>
-          <t>Suspension</t>
+          <t>Powersteering fluid top up</t>
+        </is>
+      </c>
+      <c r="D262" s="1" t="inlineStr">
+        <is>
+          <t>Manufacturers service 310,000 km</t>
         </is>
       </c>
       <c r="E262" s="3" t="n">
-        <v>598</v>
-      </c>
-      <c r="F262" t="inlineStr">
-        <is>
-          <t>Suspension City</t>
-        </is>
-      </c>
-      <c r="G262" s="32" t="inlineStr">
-        <is>
-          <t>Sqeaking noise from suspension</t>
+        <v>40</v>
+      </c>
+      <c r="F262" s="1" t="inlineStr">
+        <is>
+          <t>PW Auto Centre</t>
         </is>
       </c>
     </row>
@@ -7589,9 +7607,9 @@
       <c r="B263" s="27" t="n">
         <v>308248</v>
       </c>
-      <c r="C263" s="1" t="inlineStr">
-        <is>
-          <t>Engin oil</t>
+      <c r="C263" t="inlineStr">
+        <is>
+          <t>Brake cleaner</t>
         </is>
       </c>
       <c r="D263" s="1" t="inlineStr">
@@ -7600,7 +7618,7 @@
         </is>
       </c>
       <c r="E263" s="3" t="n">
-        <v>1495</v>
+        <v>98</v>
       </c>
       <c r="F263" s="1" t="inlineStr">
         <is>
@@ -7617,7 +7635,7 @@
       </c>
       <c r="C264" t="inlineStr">
         <is>
-          <t>O-rings</t>
+          <t>Bulbs Numberplate</t>
         </is>
       </c>
       <c r="D264" s="1" t="inlineStr">
@@ -7626,7 +7644,7 @@
         </is>
       </c>
       <c r="E264" s="3" t="n">
-        <v>155</v>
+        <v>17</v>
       </c>
       <c r="F264" s="1" t="inlineStr">
         <is>
@@ -7643,7 +7661,7 @@
       </c>
       <c r="C265" t="inlineStr">
         <is>
-          <t>Brake fluid top up</t>
+          <t>Grease propshaft</t>
         </is>
       </c>
       <c r="D265" s="1" t="inlineStr">
@@ -7652,7 +7670,7 @@
         </is>
       </c>
       <c r="E265" s="3" t="n">
-        <v>40</v>
+        <v>106</v>
       </c>
       <c r="F265" s="1" t="inlineStr">
         <is>
@@ -7669,16 +7687,16 @@
       </c>
       <c r="C266" t="inlineStr">
         <is>
-          <t>Coolant top up</t>
+          <t>Grease suspension</t>
         </is>
       </c>
       <c r="D266" s="1" t="inlineStr">
         <is>
-          <t>Cooling system</t>
+          <t>Manufacturers service 310,000 km</t>
         </is>
       </c>
       <c r="E266" s="3" t="n">
-        <v>322</v>
+        <v>106</v>
       </c>
       <c r="F266" s="1" t="inlineStr">
         <is>
@@ -7695,7 +7713,7 @@
       </c>
       <c r="C267" t="inlineStr">
         <is>
-          <t>Powersteering fluid top up</t>
+          <t>Cabin filter</t>
         </is>
       </c>
       <c r="D267" s="1" t="inlineStr">
@@ -7704,7 +7722,7 @@
         </is>
       </c>
       <c r="E267" s="3" t="n">
-        <v>40</v>
+        <v>793</v>
       </c>
       <c r="F267" s="1" t="inlineStr">
         <is>
@@ -7721,7 +7739,7 @@
       </c>
       <c r="C268" t="inlineStr">
         <is>
-          <t>Brake cleaner</t>
+          <t>Oil filter</t>
         </is>
       </c>
       <c r="D268" s="1" t="inlineStr">
@@ -7730,7 +7748,7 @@
         </is>
       </c>
       <c r="E268" s="3" t="n">
-        <v>98</v>
+        <v>793</v>
       </c>
       <c r="F268" s="1" t="inlineStr">
         <is>
@@ -7747,7 +7765,7 @@
       </c>
       <c r="C269" t="inlineStr">
         <is>
-          <t>Bulbs Numberplate</t>
+          <t>Air filter</t>
         </is>
       </c>
       <c r="D269" s="1" t="inlineStr">
@@ -7756,7 +7774,7 @@
         </is>
       </c>
       <c r="E269" s="3" t="n">
-        <v>17</v>
+        <v>793</v>
       </c>
       <c r="F269" s="1" t="inlineStr">
         <is>
@@ -7773,7 +7791,7 @@
       </c>
       <c r="C270" t="inlineStr">
         <is>
-          <t>Grease propshaft</t>
+          <t>Fuel filter</t>
         </is>
       </c>
       <c r="D270" s="1" t="inlineStr">
@@ -7782,7 +7800,7 @@
         </is>
       </c>
       <c r="E270" s="3" t="n">
-        <v>106</v>
+        <v>793</v>
       </c>
       <c r="F270" s="1" t="inlineStr">
         <is>
@@ -7799,7 +7817,7 @@
       </c>
       <c r="C271" t="inlineStr">
         <is>
-          <t>Grease suspension</t>
+          <t>Service 310,000 km</t>
         </is>
       </c>
       <c r="D271" s="1" t="inlineStr">
@@ -7808,7 +7826,7 @@
         </is>
       </c>
       <c r="E271" s="3" t="n">
-        <v>106</v>
+        <v>6622</v>
       </c>
       <c r="F271" s="1" t="inlineStr">
         <is>
@@ -7825,20 +7843,25 @@
       </c>
       <c r="C272" t="inlineStr">
         <is>
-          <t>Cabin filter</t>
-        </is>
-      </c>
-      <c r="D272" s="1" t="inlineStr">
-        <is>
-          <t>Manufacturers service 310,000 km</t>
+          <t>U-Joint (UJ-230) GUT 21</t>
+        </is>
+      </c>
+      <c r="D272" t="inlineStr">
+        <is>
+          <t>Propshaft</t>
         </is>
       </c>
       <c r="E272" s="3" t="n">
-        <v>793</v>
-      </c>
-      <c r="F272" s="1" t="inlineStr">
-        <is>
-          <t>PW Auto Centre</t>
+        <v>1124.7</v>
+      </c>
+      <c r="F272" t="inlineStr">
+        <is>
+          <t>Propshaft Engineering</t>
+        </is>
+      </c>
+      <c r="G272" s="33" t="inlineStr">
+        <is>
+          <t>Repair front propshaft. Play in U-joint. U-joint failure</t>
         </is>
       </c>
     </row>
@@ -7851,22 +7874,23 @@
       </c>
       <c r="C273" t="inlineStr">
         <is>
-          <t>Oil filter</t>
-        </is>
-      </c>
-      <c r="D273" s="1" t="inlineStr">
-        <is>
-          <t>Manufacturers service 310,000 km</t>
+          <t>Sliding Assy Gut 21</t>
+        </is>
+      </c>
+      <c r="D273" t="inlineStr">
+        <is>
+          <t>Propshaft</t>
         </is>
       </c>
       <c r="E273" s="3" t="n">
-        <v>793</v>
-      </c>
-      <c r="F273" s="1" t="inlineStr">
-        <is>
-          <t>PW Auto Centre</t>
-        </is>
-      </c>
+        <v>1901</v>
+      </c>
+      <c r="F273" t="inlineStr">
+        <is>
+          <t>Propshaft Engineering</t>
+        </is>
+      </c>
+      <c r="G273" s="34" t="n"/>
     </row>
     <row r="274">
       <c r="A274" s="2" t="n">
@@ -7877,22 +7901,23 @@
       </c>
       <c r="C274" t="inlineStr">
         <is>
-          <t>Air filter</t>
-        </is>
-      </c>
-      <c r="D274" s="1" t="inlineStr">
-        <is>
-          <t>Manufacturers service 310,000 km</t>
+          <t>Balance single shaft (CAR 2 flange)</t>
+        </is>
+      </c>
+      <c r="D274" t="inlineStr">
+        <is>
+          <t>Propshaft</t>
         </is>
       </c>
       <c r="E274" s="3" t="n">
-        <v>793</v>
-      </c>
-      <c r="F274" s="1" t="inlineStr">
-        <is>
-          <t>PW Auto Centre</t>
-        </is>
-      </c>
+        <v>443</v>
+      </c>
+      <c r="F274" t="inlineStr">
+        <is>
+          <t>Propshaft Engineering</t>
+        </is>
+      </c>
+      <c r="G274" s="34" t="n"/>
     </row>
     <row r="275">
       <c r="A275" s="2" t="n">
@@ -7903,22 +7928,23 @@
       </c>
       <c r="C275" t="inlineStr">
         <is>
-          <t>Fuel filter</t>
-        </is>
-      </c>
-      <c r="D275" s="1" t="inlineStr">
-        <is>
-          <t>Manufacturers service 310,000 km</t>
+          <t>Labour &amp; consumeables</t>
+        </is>
+      </c>
+      <c r="D275" t="inlineStr">
+        <is>
+          <t>Propshaft</t>
         </is>
       </c>
       <c r="E275" s="3" t="n">
-        <v>793</v>
-      </c>
-      <c r="F275" s="1" t="inlineStr">
-        <is>
-          <t>PW Auto Centre</t>
-        </is>
-      </c>
+        <v>816</v>
+      </c>
+      <c r="F275" t="inlineStr">
+        <is>
+          <t>Propshaft Engineering</t>
+        </is>
+      </c>
+      <c r="G275" s="35" t="n"/>
     </row>
     <row r="276">
       <c r="A276" s="2" t="n">
@@ -7929,20 +7955,25 @@
       </c>
       <c r="C276" t="inlineStr">
         <is>
-          <t>Service 310,000 km</t>
-        </is>
-      </c>
-      <c r="D276" s="1" t="inlineStr">
-        <is>
-          <t>Manufacturers service 310,000 km</t>
+          <t>Cylinder head oil sweat / slow seepage</t>
+        </is>
+      </c>
+      <c r="D276" t="inlineStr">
+        <is>
+          <t>Damage</t>
         </is>
       </c>
       <c r="E276" s="3" t="n">
-        <v>6622</v>
-      </c>
-      <c r="F276" s="1" t="inlineStr">
+        <v>0</v>
+      </c>
+      <c r="F276" t="inlineStr">
         <is>
           <t>PW Auto Centre</t>
+        </is>
+      </c>
+      <c r="G276" s="21" t="inlineStr">
+        <is>
+          <t>Block is cast iron and cylinder head is alloy - head can warp because of heat</t>
         </is>
       </c>
     </row>
@@ -7955,27 +7986,23 @@
       </c>
       <c r="C277" t="inlineStr">
         <is>
-          <t>U-Joint (UJ-230) GUT 21</t>
+          <t>Rear hub seal leak</t>
         </is>
       </c>
       <c r="D277" t="inlineStr">
         <is>
-          <t>Propshaft</t>
+          <t>Monitor</t>
         </is>
       </c>
       <c r="E277" s="3" t="n">
-        <v>1124.7</v>
+        <v>0</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
-          <t>Propshaft Engineering</t>
-        </is>
-      </c>
-      <c r="G277" s="33" t="inlineStr">
-        <is>
-          <t>Repair front propshaft. Play in U-joint. U-joint failure</t>
-        </is>
-      </c>
+          <t>PW Auto Centre</t>
+        </is>
+      </c>
+      <c r="G277" s="19" t="n"/>
     </row>
     <row r="278">
       <c r="A278" s="2" t="n">
@@ -7986,23 +8013,22 @@
       </c>
       <c r="C278" t="inlineStr">
         <is>
-          <t>Sliding Assy Gut 21</t>
+          <t>Fat knuckle grease leak</t>
         </is>
       </c>
       <c r="D278" t="inlineStr">
         <is>
-          <t>Propshaft</t>
+          <t>Monitor</t>
         </is>
       </c>
       <c r="E278" s="3" t="n">
-        <v>1901</v>
+        <v>0</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
-          <t>Propshaft Engineering</t>
-        </is>
-      </c>
-      <c r="G278" s="34" t="n"/>
+          <t>PW Auto Centre</t>
+        </is>
+      </c>
     </row>
     <row r="279">
       <c r="A279" s="2" t="n">
@@ -8013,328 +8039,325 @@
       </c>
       <c r="C279" t="inlineStr">
         <is>
-          <t>Balance single shaft (CAR 2 flange)</t>
+          <t>Waterpump - no leak detected</t>
         </is>
       </c>
       <c r="D279" t="inlineStr">
         <is>
-          <t>Propshaft</t>
+          <t>Monitor</t>
         </is>
       </c>
       <c r="E279" s="3" t="n">
-        <v>443</v>
+        <v>0</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
-          <t>Propshaft Engineering</t>
-        </is>
-      </c>
-      <c r="G279" s="34" t="n"/>
+          <t>PW Auto Centre</t>
+        </is>
+      </c>
     </row>
     <row r="280">
       <c r="A280" s="2" t="n">
-        <v>46126</v>
+        <v>46129</v>
       </c>
       <c r="B280" s="27" t="n">
-        <v>308248</v>
-      </c>
-      <c r="C280" t="inlineStr">
-        <is>
-          <t>Labour &amp; consumeables</t>
-        </is>
-      </c>
-      <c r="D280" t="inlineStr">
-        <is>
-          <t>Propshaft</t>
+        <v>308500</v>
+      </c>
+      <c r="C280" s="1" t="inlineStr">
+        <is>
+          <t>Radiator check</t>
+        </is>
+      </c>
+      <c r="D280" s="1" t="inlineStr">
+        <is>
+          <t>Cooling system</t>
         </is>
       </c>
       <c r="E280" s="3" t="n">
-        <v>816</v>
-      </c>
-      <c r="F280" t="inlineStr">
-        <is>
-          <t>Propshaft Engineering</t>
-        </is>
-      </c>
-      <c r="G280" s="35" t="n"/>
-    </row>
-    <row r="281" ht="15" customHeight="1">
+        <v>250</v>
+      </c>
+      <c r="F280" s="1" t="inlineStr">
+        <is>
+          <t>Radiator King</t>
+        </is>
+      </c>
+      <c r="G280" s="33" t="inlineStr">
+        <is>
+          <t>Testing and diagnosis of radiator &amp; cooling system. Included a checmical block test to detect combustion gases in radiator &amp; cooling system - for diagnosing head gasket, cracked head, cracked block. No issues found. All common tests for fan passed (spin by hand, visual inspection)</t>
+        </is>
+      </c>
+    </row>
+    <row r="281">
       <c r="A281" s="2" t="n">
-        <v>46126</v>
+        <v>46129</v>
       </c>
       <c r="B281" s="27" t="n">
-        <v>308248</v>
+        <v>308500</v>
       </c>
       <c r="C281" t="inlineStr">
         <is>
-          <t>Cylinder head oil sweat / slow seepage</t>
+          <t>Cooling system pressure check</t>
         </is>
       </c>
       <c r="D281" t="inlineStr">
         <is>
-          <t>Damage</t>
+          <t>Cooling system</t>
         </is>
       </c>
       <c r="E281" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="F281" t="inlineStr">
-        <is>
-          <t>PW Auto Centre</t>
-        </is>
-      </c>
-      <c r="G281" s="21" t="inlineStr">
-        <is>
-          <t>Block is cast iron and cylinder head is alloy - head can warp because of heat</t>
-        </is>
-      </c>
+      <c r="F281" s="1" t="inlineStr">
+        <is>
+          <t>Radiator King</t>
+        </is>
+      </c>
+      <c r="G281" s="34" t="n"/>
     </row>
     <row r="282">
       <c r="A282" s="2" t="n">
-        <v>46126</v>
+        <v>46129</v>
       </c>
       <c r="B282" s="27" t="n">
-        <v>308248</v>
+        <v>308500</v>
       </c>
       <c r="C282" t="inlineStr">
         <is>
-          <t>Rear hub seal leak</t>
+          <t>Chemical block test</t>
         </is>
       </c>
       <c r="D282" t="inlineStr">
         <is>
-          <t>Monitor</t>
+          <t>Cooling system</t>
         </is>
       </c>
       <c r="E282" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="F282" t="inlineStr">
-        <is>
-          <t>PW Auto Centre</t>
-        </is>
-      </c>
-      <c r="G282" s="19" t="n"/>
+      <c r="F282" s="1" t="inlineStr">
+        <is>
+          <t>Radiator King</t>
+        </is>
+      </c>
+      <c r="G282" s="34" t="n"/>
     </row>
     <row r="283">
       <c r="A283" s="2" t="n">
-        <v>46126</v>
+        <v>46129</v>
       </c>
       <c r="B283" s="27" t="n">
-        <v>308248</v>
-      </c>
-      <c r="C283" t="inlineStr">
-        <is>
-          <t>Fat knuckle grease leak</t>
-        </is>
-      </c>
-      <c r="D283" t="inlineStr">
-        <is>
-          <t>Monitor</t>
+        <v>308500</v>
+      </c>
+      <c r="C283" s="1" t="inlineStr">
+        <is>
+          <t>Fan test</t>
+        </is>
+      </c>
+      <c r="D283" s="1" t="inlineStr">
+        <is>
+          <t>Cooling system</t>
         </is>
       </c>
       <c r="E283" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="F283" t="inlineStr">
-        <is>
-          <t>PW Auto Centre</t>
-        </is>
-      </c>
+      <c r="F283" s="1" t="inlineStr">
+        <is>
+          <t>Radiator King</t>
+        </is>
+      </c>
+      <c r="G283" s="35" t="n"/>
     </row>
     <row r="284">
       <c r="A284" s="2" t="n">
-        <v>46126</v>
+        <v>46136</v>
       </c>
       <c r="B284" s="27" t="n">
-        <v>308248</v>
+        <v>308684</v>
       </c>
       <c r="C284" t="inlineStr">
         <is>
-          <t>Waterpump - no leak detected</t>
+          <t>Tyre rotation</t>
         </is>
       </c>
       <c r="D284" t="inlineStr">
         <is>
-          <t>Monitor</t>
+          <t>Tyres</t>
         </is>
       </c>
       <c r="E284" s="3" t="n">
-        <v>0</v>
+        <v>950</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
-          <t>PW Auto Centre</t>
-        </is>
-      </c>
-    </row>
-    <row r="285" ht="14" customHeight="1">
+          <t>Tiger Wheel &amp; Tyre</t>
+        </is>
+      </c>
+      <c r="G284" s="32" t="inlineStr">
+        <is>
+          <t>45,684km on tyres now</t>
+        </is>
+      </c>
+      <c r="H284" s="25" t="n"/>
+    </row>
+    <row r="285">
       <c r="A285" s="2" t="n">
-        <v>46129</v>
+        <v>46192</v>
       </c>
       <c r="B285" s="27" t="n">
-        <v>308500</v>
-      </c>
-      <c r="C285" s="1" t="inlineStr">
-        <is>
-          <t>Radiator check</t>
-        </is>
-      </c>
-      <c r="D285" s="1" t="inlineStr">
-        <is>
-          <t>Cooling system</t>
-        </is>
-      </c>
-      <c r="E285" s="3" t="n">
-        <v>250</v>
-      </c>
-      <c r="F285" s="1" t="inlineStr">
-        <is>
-          <t>Radiator King</t>
-        </is>
-      </c>
-      <c r="G285" s="33" t="inlineStr">
-        <is>
-          <t>Testing and diagnosis of radiator &amp; cooling system. Included a checmical block test to detect combustion gases in radiator &amp; cooling system - for diagnosing head gasket, cracked head, cracked block. No issues found. All common tests for fan passed (spin by hand, visual inspection)</t>
+        <v>310412</v>
+      </c>
+      <c r="C285" t="inlineStr">
+        <is>
+          <t>Injection pump rebuild kit</t>
+        </is>
+      </c>
+      <c r="D285" t="inlineStr">
+        <is>
+          <t>Injection pump</t>
+        </is>
+      </c>
+      <c r="E285" t="n">
+        <v>841.8</v>
+      </c>
+      <c r="F285" t="inlineStr">
+        <is>
+          <t>Udel Stellenbosch</t>
+        </is>
+      </c>
+      <c r="G285" s="39" t="inlineStr">
+        <is>
+          <t>Udel inv 51488 / Job 50017. Bosch VE distributor pump recon. Calibration spec Gov 093500-6070, Pump 196000-6070 Visit total R36,729.31 incl VAT (15%).</t>
         </is>
       </c>
     </row>
     <row r="286">
       <c r="A286" s="2" t="n">
-        <v>46129</v>
+        <v>46192</v>
       </c>
       <c r="B286" s="27" t="n">
-        <v>308500</v>
+        <v>310412</v>
       </c>
       <c r="C286" t="inlineStr">
         <is>
-          <t>Cooling system pressure check</t>
+          <t>Transfer (feed) pump</t>
         </is>
       </c>
       <c r="D286" t="inlineStr">
         <is>
-          <t>Cooling system</t>
-        </is>
-      </c>
-      <c r="E286" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="F286" s="1" t="inlineStr">
-        <is>
-          <t>Radiator King</t>
-        </is>
-      </c>
-      <c r="G286" s="34" t="n"/>
+          <t>Injection pump</t>
+        </is>
+      </c>
+      <c r="E286" t="n">
+        <v>1509.37</v>
+      </c>
+      <c r="F286" t="inlineStr">
+        <is>
+          <t>Udel Stellenbosch</t>
+        </is>
+      </c>
     </row>
     <row r="287">
       <c r="A287" s="2" t="n">
-        <v>46129</v>
+        <v>46192</v>
       </c>
       <c r="B287" s="27" t="n">
-        <v>308500</v>
+        <v>310412</v>
       </c>
       <c r="C287" t="inlineStr">
         <is>
-          <t>Chemical block test</t>
+          <t>Roller shoe kit</t>
         </is>
       </c>
       <c r="D287" t="inlineStr">
         <is>
-          <t>Cooling system</t>
-        </is>
-      </c>
-      <c r="E287" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="F287" s="1" t="inlineStr">
-        <is>
-          <t>Radiator King</t>
-        </is>
-      </c>
-      <c r="G287" s="34" t="n"/>
+          <t>Injection pump</t>
+        </is>
+      </c>
+      <c r="E287" t="n">
+        <v>1038.45</v>
+      </c>
+      <c r="F287" t="inlineStr">
+        <is>
+          <t>Udel Stellenbosch</t>
+        </is>
+      </c>
     </row>
     <row r="288">
       <c r="A288" s="2" t="n">
-        <v>46129</v>
+        <v>46192</v>
       </c>
       <c r="B288" s="27" t="n">
-        <v>308500</v>
-      </c>
-      <c r="C288" s="1" t="inlineStr">
-        <is>
-          <t>Fan test</t>
-        </is>
-      </c>
-      <c r="D288" s="1" t="inlineStr">
-        <is>
-          <t>Cooling system</t>
-        </is>
-      </c>
-      <c r="E288" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="F288" s="1" t="inlineStr">
-        <is>
-          <t>Radiator King</t>
-        </is>
-      </c>
-      <c r="G288" s="35" t="n"/>
+        <v>310412</v>
+      </c>
+      <c r="C288" t="inlineStr">
+        <is>
+          <t>Throttle / governor shaft</t>
+        </is>
+      </c>
+      <c r="D288" t="inlineStr">
+        <is>
+          <t>Injection pump</t>
+        </is>
+      </c>
+      <c r="E288" t="n">
+        <v>355.35</v>
+      </c>
+      <c r="F288" t="inlineStr">
+        <is>
+          <t>Udel Stellenbosch</t>
+        </is>
+      </c>
     </row>
     <row r="289">
       <c r="A289" s="2" t="n">
-        <v>46136</v>
+        <v>46192</v>
       </c>
       <c r="B289" s="27" t="n">
-        <v>308684</v>
+        <v>310412</v>
       </c>
       <c r="C289" t="inlineStr">
         <is>
-          <t>Tyre rotation</t>
+          <t>Pump front oil seal</t>
         </is>
       </c>
       <c r="D289" t="inlineStr">
         <is>
-          <t>Tyres</t>
-        </is>
-      </c>
-      <c r="E289" s="3" t="n">
-        <v>950</v>
+          <t>Injection pump</t>
+        </is>
+      </c>
+      <c r="E289" t="n">
+        <v>105.23</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
-          <t>Tiger Wheel &amp; Tyre</t>
-        </is>
-      </c>
-      <c r="G289" s="32" t="inlineStr">
-        <is>
-          <t>45,684km on tyres now</t>
-        </is>
-      </c>
-      <c r="H289" s="25" t="n"/>
+          <t>Udel Stellenbosch</t>
+        </is>
+      </c>
     </row>
     <row r="290">
       <c r="A290" s="2" t="n">
-        <v>46162</v>
+        <v>46192</v>
       </c>
       <c r="B290" s="27" t="n">
-        <v>309968</v>
-      </c>
-      <c r="C290" s="1" t="inlineStr">
-        <is>
-          <t>Free flow system (76mm 409 grade stainless stell)</t>
-        </is>
-      </c>
-      <c r="D290" s="1" t="inlineStr">
-        <is>
-          <t>Exhaust</t>
-        </is>
-      </c>
-      <c r="E290" s="3" t="n">
-        <v>8500</v>
-      </c>
-      <c r="F290" s="1" t="inlineStr">
-        <is>
-          <t>Powerflow Exhausts - Bellville</t>
+        <v>310412</v>
+      </c>
+      <c r="C290" t="inlineStr">
+        <is>
+          <t>Cam plate</t>
+        </is>
+      </c>
+      <c r="D290" t="inlineStr">
+        <is>
+          <t>Injection pump</t>
+        </is>
+      </c>
+      <c r="E290" t="n">
+        <v>401.92</v>
+      </c>
+      <c r="F290" t="inlineStr">
+        <is>
+          <t>Udel Stellenbosch</t>
         </is>
       </c>
     </row>
@@ -8347,7 +8370,7 @@
       </c>
       <c r="C291" t="inlineStr">
         <is>
-          <t>Injection pump rebuild kit</t>
+          <t>Pump mounting O-ring</t>
         </is>
       </c>
       <c r="D291" t="inlineStr">
@@ -8356,16 +8379,11 @@
         </is>
       </c>
       <c r="E291" t="n">
-        <v>841.8</v>
+        <v>124.2</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
           <t>Udel Stellenbosch</t>
-        </is>
-      </c>
-      <c r="G291" s="36" t="inlineStr">
-        <is>
-          <t>Udel inv 51488 / Job 50017. Bosch VE distributor pump recon. Calibration spec Gov 093500-6070, Pump 196000-6070 Visit total R36,729.31 incl VAT (15%).</t>
         </is>
       </c>
     </row>
@@ -8378,7 +8396,7 @@
       </c>
       <c r="C292" t="inlineStr">
         <is>
-          <t>Transfer (feed) pump</t>
+          <t>Engine cleaner</t>
         </is>
       </c>
       <c r="D292" t="inlineStr">
@@ -8387,7 +8405,7 @@
         </is>
       </c>
       <c r="E292" t="n">
-        <v>1509.37</v>
+        <v>82.8</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -8404,7 +8422,7 @@
       </c>
       <c r="C293" t="inlineStr">
         <is>
-          <t>Roller shoe kit</t>
+          <t>Sundries (pump)</t>
         </is>
       </c>
       <c r="D293" t="inlineStr">
@@ -8413,7 +8431,7 @@
         </is>
       </c>
       <c r="E293" t="n">
-        <v>1038.45</v>
+        <v>552</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -8430,7 +8448,7 @@
       </c>
       <c r="C294" t="inlineStr">
         <is>
-          <t>Throttle / governor shaft</t>
+          <t>Remove &amp; refit injection pump (labour)</t>
         </is>
       </c>
       <c r="D294" t="inlineStr">
@@ -8439,11 +8457,16 @@
         </is>
       </c>
       <c r="E294" t="n">
-        <v>355.35</v>
+        <v>5635</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
           <t>Udel Stellenbosch</t>
+        </is>
+      </c>
+      <c r="G294" t="inlineStr">
+        <is>
+          <t>Includes re-timing</t>
         </is>
       </c>
     </row>
@@ -8456,20 +8479,25 @@
       </c>
       <c r="C295" t="inlineStr">
         <is>
-          <t>Pump front oil seal</t>
+          <t>Remove, clean &amp; refit diesel tank (labour)</t>
         </is>
       </c>
       <c r="D295" t="inlineStr">
         <is>
-          <t>Injection pump</t>
+          <t>Diesel Tank</t>
         </is>
       </c>
       <c r="E295" t="n">
-        <v>105.23</v>
+        <v>2990</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
           <t>Udel Stellenbosch</t>
+        </is>
+      </c>
+      <c r="G295" t="inlineStr">
+        <is>
+          <t>Tank dropped, flushed, refitted - fuel contamination remediation</t>
         </is>
       </c>
     </row>
@@ -8482,7 +8510,7 @@
       </c>
       <c r="C296" t="inlineStr">
         <is>
-          <t>Cam plate</t>
+          <t>Labour to recondition injection pump</t>
         </is>
       </c>
       <c r="D296" t="inlineStr">
@@ -8491,11 +8519,16 @@
         </is>
       </c>
       <c r="E296" t="n">
-        <v>401.92</v>
+        <v>4715</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
           <t>Udel Stellenbosch</t>
+        </is>
+      </c>
+      <c r="G296" t="inlineStr">
+        <is>
+          <t>Bench rebuild &amp; calibration</t>
         </is>
       </c>
     </row>
@@ -8508,20 +8541,25 @@
       </c>
       <c r="C297" t="inlineStr">
         <is>
-          <t>Pump mounting O-ring</t>
+          <t>Injector nozzles x6</t>
         </is>
       </c>
       <c r="D297" t="inlineStr">
         <is>
-          <t>Injection pump</t>
+          <t>Injectors</t>
         </is>
       </c>
       <c r="E297" t="n">
-        <v>124.2</v>
+        <v>4183.99</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
           <t>Udel Stellenbosch</t>
+        </is>
+      </c>
+      <c r="G297" t="inlineStr">
+        <is>
+          <t>All 6 nozzles renewed; injectors bench pop-tested</t>
         </is>
       </c>
     </row>
@@ -8534,16 +8572,16 @@
       </c>
       <c r="C298" t="inlineStr">
         <is>
-          <t>Engine cleaner</t>
+          <t>Brass (seat) washers x6</t>
         </is>
       </c>
       <c r="D298" t="inlineStr">
         <is>
-          <t>Injection pump</t>
+          <t>Injectors</t>
         </is>
       </c>
       <c r="E298" t="n">
-        <v>82.8</v>
+        <v>289.8</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -8560,16 +8598,16 @@
       </c>
       <c r="C299" t="inlineStr">
         <is>
-          <t>Sundries (pump)</t>
+          <t>Return (leak-off) washers x6</t>
         </is>
       </c>
       <c r="D299" t="inlineStr">
         <is>
-          <t>Injection pump</t>
+          <t>Injectors</t>
         </is>
       </c>
       <c r="E299" t="n">
-        <v>552</v>
+        <v>165.6</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -8586,25 +8624,20 @@
       </c>
       <c r="C300" t="inlineStr">
         <is>
-          <t>Remove &amp; refit injection pump (labour)</t>
+          <t>Injector heat shields x6</t>
         </is>
       </c>
       <c r="D300" t="inlineStr">
         <is>
-          <t>Injection pump</t>
+          <t>Injectors</t>
         </is>
       </c>
       <c r="E300" t="n">
-        <v>5635</v>
+        <v>186.3</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
           <t>Udel Stellenbosch</t>
-        </is>
-      </c>
-      <c r="G300" t="inlineStr">
-        <is>
-          <t>Includes re-timing</t>
         </is>
       </c>
     </row>
@@ -8617,25 +8650,20 @@
       </c>
       <c r="C301" t="inlineStr">
         <is>
-          <t>Remove, clean &amp; refit diesel tank (labour)</t>
+          <t>Fuel filter housing</t>
         </is>
       </c>
       <c r="D301" t="inlineStr">
         <is>
-          <t>Diesel Tank</t>
+          <t>Injectors</t>
         </is>
       </c>
       <c r="E301" t="n">
-        <v>2990</v>
+        <v>2140.47</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
           <t>Udel Stellenbosch</t>
-        </is>
-      </c>
-      <c r="G301" t="inlineStr">
-        <is>
-          <t>Tank dropped, flushed, refitted - fuel contamination remediation</t>
         </is>
       </c>
     </row>
@@ -8648,25 +8676,20 @@
       </c>
       <c r="C302" t="inlineStr">
         <is>
-          <t>Labour to recondition injection pump</t>
+          <t>Diesel fuel filter</t>
         </is>
       </c>
       <c r="D302" t="inlineStr">
         <is>
-          <t>Injection pump</t>
+          <t>Injectors</t>
         </is>
       </c>
       <c r="E302" t="n">
-        <v>4715</v>
+        <v>1164.38</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
           <t>Udel Stellenbosch</t>
-        </is>
-      </c>
-      <c r="G302" t="inlineStr">
-        <is>
-          <t>Bench rebuild &amp; calibration</t>
         </is>
       </c>
     </row>
@@ -8679,7 +8702,7 @@
       </c>
       <c r="C303" t="inlineStr">
         <is>
-          <t>Injector nozzles x6</t>
+          <t>Intercooler gasket</t>
         </is>
       </c>
       <c r="D303" t="inlineStr">
@@ -8688,7 +8711,7 @@
         </is>
       </c>
       <c r="E303" t="n">
-        <v>4183.99</v>
+        <v>179.4</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -8697,7 +8720,7 @@
       </c>
       <c r="G303" t="inlineStr">
         <is>
-          <t>All 6 nozzles renewed; injectors bench pop-tested</t>
+          <t>Disturbed during access</t>
         </is>
       </c>
     </row>
@@ -8710,7 +8733,7 @@
       </c>
       <c r="C304" t="inlineStr">
         <is>
-          <t>Brass (seat) washers x6</t>
+          <t>Sundries (injectors)</t>
         </is>
       </c>
       <c r="D304" t="inlineStr">
@@ -8719,7 +8742,7 @@
         </is>
       </c>
       <c r="E304" t="n">
-        <v>289.8</v>
+        <v>483</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -8736,7 +8759,7 @@
       </c>
       <c r="C305" t="inlineStr">
         <is>
-          <t>Return (leak-off) washers x6</t>
+          <t>Remove &amp; refit injectors &amp; bench test (labour)</t>
         </is>
       </c>
       <c r="D305" t="inlineStr">
@@ -8745,7 +8768,7 @@
         </is>
       </c>
       <c r="E305" t="n">
-        <v>165.6</v>
+        <v>2242.5</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -8762,7 +8785,7 @@
       </c>
       <c r="C306" t="inlineStr">
         <is>
-          <t>Injector heat shields x6</t>
+          <t>Labour to recondition injectors (incl. glow plugs)</t>
         </is>
       </c>
       <c r="D306" t="inlineStr">
@@ -8771,7 +8794,7 @@
         </is>
       </c>
       <c r="E306" t="n">
-        <v>186.3</v>
+        <v>2415</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -8788,20 +8811,25 @@
       </c>
       <c r="C307" t="inlineStr">
         <is>
-          <t>Fuel filter housing</t>
+          <t>Valve adjustment shims x12</t>
         </is>
       </c>
       <c r="D307" t="inlineStr">
         <is>
-          <t>Injectors</t>
+          <t>Valves</t>
         </is>
       </c>
       <c r="E307" t="n">
-        <v>2140.47</v>
+        <v>1242</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
           <t>Udel Stellenbosch</t>
+        </is>
+      </c>
+      <c r="G307" t="inlineStr">
+        <is>
+          <t>12-valve head - one shim per valve</t>
         </is>
       </c>
     </row>
@@ -8814,16 +8842,16 @@
       </c>
       <c r="C308" t="inlineStr">
         <is>
-          <t>Diesel fuel filter</t>
+          <t>Sundries (valves)</t>
         </is>
       </c>
       <c r="D308" t="inlineStr">
         <is>
-          <t>Injectors</t>
+          <t>Valves</t>
         </is>
       </c>
       <c r="E308" t="n">
-        <v>1164.38</v>
+        <v>322</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -8840,268 +8868,63 @@
       </c>
       <c r="C309" t="inlineStr">
         <is>
-          <t>Intercooler gasket</t>
+          <t>Labour to set valve clearances</t>
         </is>
       </c>
       <c r="D309" t="inlineStr">
         <is>
-          <t>Injectors</t>
+          <t>Valves</t>
         </is>
       </c>
       <c r="E309" t="n">
-        <v>179.4</v>
+        <v>3363.75</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
           <t>Udel Stellenbosch</t>
-        </is>
-      </c>
-      <c r="G309" t="inlineStr">
-        <is>
-          <t>Disturbed during access</t>
         </is>
       </c>
     </row>
     <row r="310">
       <c r="A310" s="2" t="n">
-        <v>46192</v>
+        <v>46238</v>
       </c>
       <c r="B310" s="27" t="n">
-        <v>310412</v>
-      </c>
-      <c r="C310" t="inlineStr">
-        <is>
-          <t>Sundries (injectors)</t>
+        <v>311263</v>
+      </c>
+      <c r="C310" s="1" t="inlineStr">
+        <is>
+          <t>Battery - starter</t>
         </is>
       </c>
       <c r="D310" t="inlineStr">
         <is>
-          <t>Injectors</t>
-        </is>
-      </c>
-      <c r="E310" t="n">
-        <v>483</v>
-      </c>
-      <c r="F310" t="inlineStr">
-        <is>
-          <t>Udel Stellenbosch</t>
-        </is>
-      </c>
-    </row>
-    <row r="311">
-      <c r="A311" s="2" t="n">
-        <v>46192</v>
-      </c>
-      <c r="B311" s="27" t="n">
-        <v>310412</v>
-      </c>
-      <c r="C311" t="inlineStr">
-        <is>
-          <t>Remove &amp; refit injectors &amp; bench test (labour)</t>
-        </is>
-      </c>
-      <c r="D311" t="inlineStr">
-        <is>
-          <t>Injectors</t>
-        </is>
-      </c>
-      <c r="E311" t="n">
-        <v>2242.5</v>
-      </c>
-      <c r="F311" t="inlineStr">
-        <is>
-          <t>Udel Stellenbosch</t>
-        </is>
-      </c>
-    </row>
-    <row r="312">
-      <c r="A312" s="2" t="n">
-        <v>46192</v>
-      </c>
-      <c r="B312" s="27" t="n">
-        <v>310412</v>
-      </c>
-      <c r="C312" t="inlineStr">
-        <is>
-          <t>Labour to recondition injectors (incl. glow plugs)</t>
-        </is>
-      </c>
-      <c r="D312" t="inlineStr">
-        <is>
-          <t>Injectors</t>
-        </is>
-      </c>
-      <c r="E312" t="n">
-        <v>2415</v>
-      </c>
-      <c r="F312" t="inlineStr">
-        <is>
-          <t>Udel Stellenbosch</t>
-        </is>
-      </c>
-    </row>
-    <row r="313">
-      <c r="A313" s="2" t="n">
-        <v>46192</v>
-      </c>
-      <c r="B313" s="27" t="n">
-        <v>310412</v>
-      </c>
-      <c r="C313" t="inlineStr">
-        <is>
-          <t>Valve adjustment shims x12</t>
-        </is>
-      </c>
-      <c r="D313" t="inlineStr">
-        <is>
-          <t>Valves</t>
-        </is>
-      </c>
-      <c r="E313" t="n">
-        <v>1242</v>
-      </c>
-      <c r="F313" t="inlineStr">
-        <is>
-          <t>Udel Stellenbosch</t>
-        </is>
-      </c>
-      <c r="G313" t="inlineStr">
-        <is>
-          <t>12-valve head - one shim per valve</t>
-        </is>
-      </c>
-    </row>
-    <row r="314">
-      <c r="A314" s="2" t="n">
-        <v>46192</v>
-      </c>
-      <c r="B314" s="27" t="n">
-        <v>310412</v>
-      </c>
-      <c r="C314" t="inlineStr">
-        <is>
-          <t>Sundries (valves)</t>
-        </is>
-      </c>
-      <c r="D314" t="inlineStr">
-        <is>
-          <t>Valves</t>
-        </is>
-      </c>
-      <c r="E314" t="n">
-        <v>322</v>
-      </c>
-      <c r="F314" t="inlineStr">
-        <is>
-          <t>Udel Stellenbosch</t>
-        </is>
-      </c>
-    </row>
-    <row r="315">
-      <c r="A315" s="2" t="n">
-        <v>46192</v>
-      </c>
-      <c r="B315" s="27" t="n">
-        <v>310412</v>
-      </c>
-      <c r="C315" t="inlineStr">
-        <is>
-          <t>Labour to set valve clearances</t>
-        </is>
-      </c>
-      <c r="D315" t="inlineStr">
-        <is>
-          <t>Valves</t>
-        </is>
-      </c>
-      <c r="E315" t="n">
-        <v>3363.75</v>
-      </c>
-      <c r="F315" t="inlineStr">
-        <is>
-          <t>Udel Stellenbosch</t>
-        </is>
-      </c>
-    </row>
-    <row r="316">
-      <c r="A316" s="2" t="inlineStr">
-        <is>
-          <t>Jul 2026 (TBC)</t>
-        </is>
-      </c>
-      <c r="B316" s="27" t="n">
-        <v>311000</v>
-      </c>
-      <c r="C316" t="inlineStr">
-        <is>
-          <t>All-Victron LiFePO4 electrical system — full install</t>
-        </is>
-      </c>
-      <c r="D316" t="inlineStr">
-        <is>
-          <t>Electrical</t>
-        </is>
-      </c>
-      <c r="E316" t="inlineStr">
-        <is>
-          <t>TBC</t>
-        </is>
-      </c>
-      <c r="F316" t="inlineStr">
+          <t>Battery</t>
+        </is>
+      </c>
+      <c r="E310" s="3" t="n">
+        <v>2637.33</v>
+      </c>
+      <c r="F310" s="1" t="inlineStr">
         <is>
           <t>Manjaro Industries</t>
         </is>
       </c>
-      <c r="G316" t="inlineStr">
-        <is>
-          <t>Per quote LC76SW004 — invoice date &amp; final cost TO CONFIRM. Enertec Power+ 210Ah LiFePO4 house battery; Victron Orion 12/12-50 DC-DC (~40A cap); MultiPlus 12/500/20-16; SmartSolar MPPT 100/30; SmartShunt 500A; BatteryProtect 65A; Safety Hub 150 + battery switch; 16A shore inlet; DEFA removed. Willard 650 crank unchanged.</t>
-        </is>
-      </c>
-    </row>
-    <row r="317">
-      <c r="A317" s="2" t="n">
-        <v>46238</v>
-      </c>
-      <c r="B317" s="27" t="n">
-        <v>311263</v>
-      </c>
-      <c r="C317" s="1" t="inlineStr">
-        <is>
-          <t>Battery - starter</t>
-        </is>
-      </c>
-      <c r="D317" t="inlineStr">
-        <is>
-          <t>Battery</t>
-        </is>
-      </c>
-      <c r="E317" s="3" t="inlineStr">
-        <is>
-          <t>TBC</t>
-        </is>
-      </c>
-      <c r="F317" s="1" t="n"/>
-      <c r="G317" t="inlineStr">
-        <is>
-          <t>Enertec 650B-BLS Premium Plus Silver — SMF (sealed calcium), 92 Ah, 750 CCA SAE / 680 EN. Replaced the Willard 650 (fitted 23 Jan 2025 @ 271,056 km). Cost TO CONFIRM.</t>
+      <c r="G310" t="inlineStr">
+        <is>
+          <t>Enertec 650B-BLS Premium Plus Silver SMF crank battery + delivery. Invoice LC76SW004 (VAT-incl: R2,133.33 + R160.00 delivery, excl, ×1.15). Replaces Willard 650. Service item (consumable).</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G289"/>
   <mergeCells count="5">
-    <mergeCell ref="G285:G288"/>
-    <mergeCell ref="G277:G280"/>
-    <mergeCell ref="G171:G199"/>
+    <mergeCell ref="G272:G275"/>
     <mergeCell ref="G97:G100"/>
-    <mergeCell ref="G291:G292"/>
+    <mergeCell ref="G280:G283"/>
+    <mergeCell ref="G170:G198"/>
+    <mergeCell ref="G285:G286"/>
   </mergeCells>
-  <printOptions headings="1"/>
-  <pageMargins left="0.1968503937007874" right="0" top="0.1968503937007874" bottom="0.1968503937007874" header="0.3149606299212598" footer="0.3149606299212598"/>
-  <pageSetup orientation="landscape" paperSize="9" scale="50" fitToHeight="2" horizontalDpi="0" verticalDpi="0"/>
-  <rowBreaks count="1" manualBreakCount="1">
-    <brk id="80" min="0" max="16383" man="1"/>
-  </rowBreaks>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
@@ -9769,4 +9592,2036 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:K48"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="46" customWidth="1" min="1" max="1"/>
+    <col width="32" customWidth="1" min="2" max="2"/>
+    <col width="24" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="10" customWidth="1" min="5" max="5"/>
+    <col width="13" customWidth="1" min="6" max="6"/>
+    <col width="15" customWidth="1" min="7" max="7"/>
+    <col width="20" customWidth="1" min="8" max="8"/>
+    <col width="12" customWidth="1" min="9" max="9"/>
+    <col width="13" customWidth="1" min="10" max="10"/>
+    <col width="64" customWidth="1" min="11" max="11"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="40" t="inlineStr">
+        <is>
+          <t>Item</t>
+        </is>
+      </c>
+      <c r="B1" s="40" t="inlineStr">
+        <is>
+          <t>Category</t>
+        </is>
+      </c>
+      <c r="C1" s="40" t="inlineStr">
+        <is>
+          <t>Supplier</t>
+        </is>
+      </c>
+      <c r="D1" s="40" t="inlineStr">
+        <is>
+          <t>Date</t>
+        </is>
+      </c>
+      <c r="E1" s="40" t="inlineStr">
+        <is>
+          <t>Odometer</t>
+        </is>
+      </c>
+      <c r="F1" s="40" t="inlineStr">
+        <is>
+          <t>Invoice ref</t>
+        </is>
+      </c>
+      <c r="G1" s="40" t="inlineStr">
+        <is>
+          <t>Fitment type</t>
+        </is>
+      </c>
+      <c r="H1" s="40" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+      <c r="I1" s="40" t="inlineStr">
+        <is>
+          <t>Basis</t>
+        </is>
+      </c>
+      <c r="J1" s="40" t="inlineStr">
+        <is>
+          <t>Amount (R)</t>
+        </is>
+      </c>
+      <c r="K1" s="40" t="inlineStr">
+        <is>
+          <t>Notes</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="41" t="inlineStr">
+        <is>
+          <t>Multi Media Unit (Mid Spect TT) with Butterfly camera</t>
+        </is>
+      </c>
+      <c r="B2" s="41" t="inlineStr">
+        <is>
+          <t>Infotainment</t>
+        </is>
+      </c>
+      <c r="C2" s="41" t="inlineStr">
+        <is>
+          <t>Musical Cars</t>
+        </is>
+      </c>
+      <c r="D2" s="42" t="n">
+        <v>45593</v>
+      </c>
+      <c r="E2" s="43" t="n">
+        <v>262000</v>
+      </c>
+      <c r="F2" s="41" t="inlineStr"/>
+      <c r="G2" s="41" t="inlineStr">
+        <is>
+          <t>Permanent</t>
+        </is>
+      </c>
+      <c r="H2" s="41" t="inlineStr">
+        <is>
+          <t>Fitted</t>
+        </is>
+      </c>
+      <c r="I2" s="41" t="inlineStr">
+        <is>
+          <t>Cost</t>
+        </is>
+      </c>
+      <c r="J2" s="44" t="n">
+        <v>7000</v>
+      </c>
+      <c r="K2" s="41" t="inlineStr">
+        <is>
+          <t>Head unit + reversing camera. Reclassified from Services.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="41" t="inlineStr">
+        <is>
+          <t>TPMS (TP-V31) Solar Powered Internal)</t>
+        </is>
+      </c>
+      <c r="B3" s="41" t="inlineStr">
+        <is>
+          <t>Tyre monitoring</t>
+        </is>
+      </c>
+      <c r="C3" s="41" t="inlineStr">
+        <is>
+          <t>First Alignment</t>
+        </is>
+      </c>
+      <c r="D3" s="42" t="n">
+        <v>45782</v>
+      </c>
+      <c r="E3" s="43" t="n">
+        <v>274000</v>
+      </c>
+      <c r="F3" s="41" t="inlineStr"/>
+      <c r="G3" s="41" t="inlineStr">
+        <is>
+          <t>Permanent</t>
+        </is>
+      </c>
+      <c r="H3" s="41" t="inlineStr">
+        <is>
+          <t>Fitted</t>
+        </is>
+      </c>
+      <c r="I3" s="41" t="inlineStr">
+        <is>
+          <t>Cost</t>
+        </is>
+      </c>
+      <c r="J3" s="44" t="n">
+        <v>3450</v>
+      </c>
+      <c r="K3" s="41" t="inlineStr">
+        <is>
+          <t>SteelMate TP-V31 solar internal TPMS. Reclassified from Services.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="41" t="inlineStr">
+        <is>
+          <t>Victron Cyrix 120A isolator</t>
+        </is>
+      </c>
+      <c r="B4" s="41" t="inlineStr">
+        <is>
+          <t>Electrical (dual-battery, superseded)</t>
+        </is>
+      </c>
+      <c r="C4" s="41" t="inlineStr">
+        <is>
+          <t>HBC Systems</t>
+        </is>
+      </c>
+      <c r="D4" s="42" t="n">
+        <v>46043</v>
+      </c>
+      <c r="E4" s="43" t="n">
+        <v>294000</v>
+      </c>
+      <c r="F4" s="41" t="inlineStr"/>
+      <c r="G4" s="41" t="inlineStr">
+        <is>
+          <t>Permanent</t>
+        </is>
+      </c>
+      <c r="H4" s="41" t="inlineStr">
+        <is>
+          <t>Removed-superseded</t>
+        </is>
+      </c>
+      <c r="I4" s="41" t="inlineStr">
+        <is>
+          <t>Cost</t>
+        </is>
+      </c>
+      <c r="J4" s="44" t="n">
+        <v>1140</v>
+      </c>
+      <c r="K4" s="41" t="inlineStr">
+        <is>
+          <t>Old dual-battery build; removed at LiFePO4 install Aug 2026. Excluded from insurance value.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="41" t="inlineStr">
+        <is>
+          <t>BM2000 dual-battery monitor</t>
+        </is>
+      </c>
+      <c r="B5" s="41" t="inlineStr">
+        <is>
+          <t>Electrical (dual-battery, superseded)</t>
+        </is>
+      </c>
+      <c r="C5" s="41" t="inlineStr">
+        <is>
+          <t>HBC Systems</t>
+        </is>
+      </c>
+      <c r="D5" s="42" t="n">
+        <v>46043</v>
+      </c>
+      <c r="E5" s="43" t="n">
+        <v>294000</v>
+      </c>
+      <c r="F5" s="41" t="inlineStr"/>
+      <c r="G5" s="41" t="inlineStr">
+        <is>
+          <t>Permanent</t>
+        </is>
+      </c>
+      <c r="H5" s="41" t="inlineStr">
+        <is>
+          <t>Removed-superseded</t>
+        </is>
+      </c>
+      <c r="I5" s="41" t="inlineStr">
+        <is>
+          <t>Cost</t>
+        </is>
+      </c>
+      <c r="J5" s="44" t="n">
+        <v>684</v>
+      </c>
+      <c r="K5" s="41" t="inlineStr">
+        <is>
+          <t>Superseded by BMV-712. Excluded from insurance value.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="41" t="inlineStr">
+        <is>
+          <t>Fitment labour (old dual-battery)</t>
+        </is>
+      </c>
+      <c r="B6" s="41" t="inlineStr">
+        <is>
+          <t>Electrical (dual-battery, superseded)</t>
+        </is>
+      </c>
+      <c r="C6" s="41" t="inlineStr">
+        <is>
+          <t>HBC Systems</t>
+        </is>
+      </c>
+      <c r="D6" s="42" t="n">
+        <v>46043</v>
+      </c>
+      <c r="E6" s="43" t="n">
+        <v>294000</v>
+      </c>
+      <c r="F6" s="41" t="inlineStr"/>
+      <c r="G6" s="41" t="inlineStr">
+        <is>
+          <t>Permanent</t>
+        </is>
+      </c>
+      <c r="H6" s="41" t="inlineStr">
+        <is>
+          <t>Removed-superseded</t>
+        </is>
+      </c>
+      <c r="I6" s="41" t="inlineStr">
+        <is>
+          <t>Cost</t>
+        </is>
+      </c>
+      <c r="J6" s="44" t="n">
+        <v>597</v>
+      </c>
+      <c r="K6" s="41" t="inlineStr">
+        <is>
+          <t>Superseded.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="41" t="inlineStr">
+        <is>
+          <t>Free flow system (76mm 409 grade stainless stell)</t>
+        </is>
+      </c>
+      <c r="B7" s="41" t="inlineStr">
+        <is>
+          <t>Exhaust (free-flow upgrade)</t>
+        </is>
+      </c>
+      <c r="C7" s="41" t="inlineStr">
+        <is>
+          <t>Powerflow Exhausts - Bellville</t>
+        </is>
+      </c>
+      <c r="D7" s="42" t="n">
+        <v>46162</v>
+      </c>
+      <c r="E7" s="43" t="n">
+        <v>309968</v>
+      </c>
+      <c r="F7" s="41" t="inlineStr"/>
+      <c r="G7" s="41" t="inlineStr">
+        <is>
+          <t>Permanent</t>
+        </is>
+      </c>
+      <c r="H7" s="41" t="inlineStr">
+        <is>
+          <t>Fitted</t>
+        </is>
+      </c>
+      <c r="I7" s="41" t="inlineStr">
+        <is>
+          <t>Cost</t>
+        </is>
+      </c>
+      <c r="J7" s="44" t="n">
+        <v>8500</v>
+      </c>
+      <c r="K7" s="41" t="inlineStr">
+        <is>
+          <t>76mm 409-grade stainless free-flow. Capability upgrade. Reclassified from Services.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="41" t="inlineStr">
+        <is>
+          <t>Manjaro build — Requirements</t>
+        </is>
+      </c>
+      <c r="B8" s="41" t="inlineStr">
+        <is>
+          <t>Manjaro build</t>
+        </is>
+      </c>
+      <c r="C8" s="41" t="inlineStr">
+        <is>
+          <t>Manjaro Industries</t>
+        </is>
+      </c>
+      <c r="D8" s="42" t="n">
+        <v>46240</v>
+      </c>
+      <c r="E8" s="43" t="n">
+        <v>311263</v>
+      </c>
+      <c r="F8" s="41" t="inlineStr">
+        <is>
+          <t>LC76SW004</t>
+        </is>
+      </c>
+      <c r="G8" s="41" t="inlineStr">
+        <is>
+          <t>Permanent</t>
+        </is>
+      </c>
+      <c r="H8" s="41" t="inlineStr">
+        <is>
+          <t>Fitted</t>
+        </is>
+      </c>
+      <c r="I8" s="41" t="inlineStr">
+        <is>
+          <t>Cost</t>
+        </is>
+      </c>
+      <c r="J8" s="44" t="n">
+        <v>7132.13</v>
+      </c>
+      <c r="K8" s="41" t="inlineStr">
+        <is>
+          <t>Invoice LC76SW004. VAT-incl (excl R6,201.85 ×1.15).</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="41" t="inlineStr">
+        <is>
+          <t>Manjaro build — Rear</t>
+        </is>
+      </c>
+      <c r="B9" s="41" t="inlineStr">
+        <is>
+          <t>Manjaro build</t>
+        </is>
+      </c>
+      <c r="C9" s="41" t="inlineStr">
+        <is>
+          <t>Manjaro Industries</t>
+        </is>
+      </c>
+      <c r="D9" s="42" t="n">
+        <v>46240</v>
+      </c>
+      <c r="E9" s="43" t="n">
+        <v>311263</v>
+      </c>
+      <c r="F9" s="41" t="inlineStr">
+        <is>
+          <t>LC76SW004</t>
+        </is>
+      </c>
+      <c r="G9" s="41" t="inlineStr">
+        <is>
+          <t>Permanent</t>
+        </is>
+      </c>
+      <c r="H9" s="41" t="inlineStr">
+        <is>
+          <t>Fitted</t>
+        </is>
+      </c>
+      <c r="I9" s="41" t="inlineStr">
+        <is>
+          <t>Cost</t>
+        </is>
+      </c>
+      <c r="J9" s="44" t="n">
+        <v>70956</v>
+      </c>
+      <c r="K9" s="41" t="inlineStr">
+        <is>
+          <t>Invoice LC76SW004. VAT-incl (excl R61,700.87 ×1.15). Includes integrated GobiX tow hitch (replaced the removed original tow bar).</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="41" t="inlineStr">
+        <is>
+          <t>Manjaro build — Interior Front</t>
+        </is>
+      </c>
+      <c r="B10" s="41" t="inlineStr">
+        <is>
+          <t>Manjaro build</t>
+        </is>
+      </c>
+      <c r="C10" s="41" t="inlineStr">
+        <is>
+          <t>Manjaro Industries</t>
+        </is>
+      </c>
+      <c r="D10" s="42" t="n">
+        <v>46240</v>
+      </c>
+      <c r="E10" s="43" t="n">
+        <v>311263</v>
+      </c>
+      <c r="F10" s="41" t="inlineStr">
+        <is>
+          <t>LC76SW004</t>
+        </is>
+      </c>
+      <c r="G10" s="41" t="inlineStr">
+        <is>
+          <t>Permanent</t>
+        </is>
+      </c>
+      <c r="H10" s="41" t="inlineStr">
+        <is>
+          <t>Fitted</t>
+        </is>
+      </c>
+      <c r="I10" s="41" t="inlineStr">
+        <is>
+          <t>Cost</t>
+        </is>
+      </c>
+      <c r="J10" s="44" t="n">
+        <v>17517.42</v>
+      </c>
+      <c r="K10" s="41" t="inlineStr">
+        <is>
+          <t>Invoice LC76SW004. VAT-incl (excl R15,232.54 ×1.15).</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="41" t="inlineStr">
+        <is>
+          <t>Manjaro build — Interior Rear</t>
+        </is>
+      </c>
+      <c r="B11" s="41" t="inlineStr">
+        <is>
+          <t>Manjaro build</t>
+        </is>
+      </c>
+      <c r="C11" s="41" t="inlineStr">
+        <is>
+          <t>Manjaro Industries</t>
+        </is>
+      </c>
+      <c r="D11" s="42" t="n">
+        <v>46240</v>
+      </c>
+      <c r="E11" s="43" t="n">
+        <v>311263</v>
+      </c>
+      <c r="F11" s="41" t="inlineStr">
+        <is>
+          <t>LC76SW004</t>
+        </is>
+      </c>
+      <c r="G11" s="41" t="inlineStr">
+        <is>
+          <t>Permanent</t>
+        </is>
+      </c>
+      <c r="H11" s="41" t="inlineStr">
+        <is>
+          <t>Fitted</t>
+        </is>
+      </c>
+      <c r="I11" s="41" t="inlineStr">
+        <is>
+          <t>Cost</t>
+        </is>
+      </c>
+      <c r="J11" s="44" t="n">
+        <v>94718.39</v>
+      </c>
+      <c r="K11" s="41" t="inlineStr">
+        <is>
+          <t>Invoice LC76SW004. VAT-incl (excl R82,363.82 ×1.15). Includes integrated GobiX tow hitch (replaced the removed original tow bar).</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="41" t="inlineStr">
+        <is>
+          <t>Manjaro build — Engine Bay</t>
+        </is>
+      </c>
+      <c r="B12" s="41" t="inlineStr">
+        <is>
+          <t>Manjaro build</t>
+        </is>
+      </c>
+      <c r="C12" s="41" t="inlineStr">
+        <is>
+          <t>Manjaro Industries</t>
+        </is>
+      </c>
+      <c r="D12" s="42" t="n">
+        <v>46240</v>
+      </c>
+      <c r="E12" s="43" t="n">
+        <v>311263</v>
+      </c>
+      <c r="F12" s="41" t="inlineStr">
+        <is>
+          <t>LC76SW004</t>
+        </is>
+      </c>
+      <c r="G12" s="41" t="inlineStr">
+        <is>
+          <t>Permanent</t>
+        </is>
+      </c>
+      <c r="H12" s="41" t="inlineStr">
+        <is>
+          <t>Fitted</t>
+        </is>
+      </c>
+      <c r="I12" s="41" t="inlineStr">
+        <is>
+          <t>Cost</t>
+        </is>
+      </c>
+      <c r="J12" s="44" t="n">
+        <v>12046.34</v>
+      </c>
+      <c r="K12" s="41" t="inlineStr">
+        <is>
+          <t>Invoice LC76SW004. VAT-incl (excl R10,475.08 ×1.15).</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="41" t="inlineStr">
+        <is>
+          <t>Manjaro build — Fire kit</t>
+        </is>
+      </c>
+      <c r="B13" s="41" t="inlineStr">
+        <is>
+          <t>Manjaro build</t>
+        </is>
+      </c>
+      <c r="C13" s="41" t="inlineStr">
+        <is>
+          <t>Manjaro Industries</t>
+        </is>
+      </c>
+      <c r="D13" s="42" t="n">
+        <v>46240</v>
+      </c>
+      <c r="E13" s="43" t="n">
+        <v>311263</v>
+      </c>
+      <c r="F13" s="41" t="inlineStr">
+        <is>
+          <t>LC76SW004</t>
+        </is>
+      </c>
+      <c r="G13" s="41" t="inlineStr">
+        <is>
+          <t>Removable</t>
+        </is>
+      </c>
+      <c r="H13" s="41" t="inlineStr">
+        <is>
+          <t>Fitted</t>
+        </is>
+      </c>
+      <c r="I13" s="41" t="inlineStr">
+        <is>
+          <t>Cost</t>
+        </is>
+      </c>
+      <c r="J13" s="44" t="n">
+        <v>5574</v>
+      </c>
+      <c r="K13" s="41" t="inlineStr">
+        <is>
+          <t>Invoice LC76SW004. VAT-incl (excl R4,846.96 ×1.15).</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="41" t="inlineStr">
+        <is>
+          <t>Manjaro build — Electrical (LiFePO4 system)</t>
+        </is>
+      </c>
+      <c r="B14" s="41" t="inlineStr">
+        <is>
+          <t>Manjaro build</t>
+        </is>
+      </c>
+      <c r="C14" s="41" t="inlineStr">
+        <is>
+          <t>Manjaro Industries</t>
+        </is>
+      </c>
+      <c r="D14" s="42" t="n">
+        <v>46240</v>
+      </c>
+      <c r="E14" s="43" t="n">
+        <v>311263</v>
+      </c>
+      <c r="F14" s="41" t="inlineStr">
+        <is>
+          <t>LC76SW004</t>
+        </is>
+      </c>
+      <c r="G14" s="41" t="inlineStr">
+        <is>
+          <t>Permanent</t>
+        </is>
+      </c>
+      <c r="H14" s="41" t="inlineStr">
+        <is>
+          <t>Fitted</t>
+        </is>
+      </c>
+      <c r="I14" s="41" t="inlineStr">
+        <is>
+          <t>Cost</t>
+        </is>
+      </c>
+      <c r="J14" s="44" t="n">
+        <v>52425.53</v>
+      </c>
+      <c r="K14" s="41" t="inlineStr">
+        <is>
+          <t>Invoice LC76SW004. VAT-incl (excl R45,587.42 ×1.15).</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="41" t="inlineStr">
+        <is>
+          <t>Manjaro build — Extras</t>
+        </is>
+      </c>
+      <c r="B15" s="41" t="inlineStr">
+        <is>
+          <t>Manjaro build</t>
+        </is>
+      </c>
+      <c r="C15" s="41" t="inlineStr">
+        <is>
+          <t>Manjaro Industries</t>
+        </is>
+      </c>
+      <c r="D15" s="42" t="n">
+        <v>46240</v>
+      </c>
+      <c r="E15" s="43" t="n">
+        <v>311263</v>
+      </c>
+      <c r="F15" s="41" t="inlineStr">
+        <is>
+          <t>LC76SW004</t>
+        </is>
+      </c>
+      <c r="G15" s="41" t="inlineStr">
+        <is>
+          <t>Removable</t>
+        </is>
+      </c>
+      <c r="H15" s="41" t="inlineStr">
+        <is>
+          <t>Fitted</t>
+        </is>
+      </c>
+      <c r="I15" s="41" t="inlineStr">
+        <is>
+          <t>Cost</t>
+        </is>
+      </c>
+      <c r="J15" s="44" t="n">
+        <v>15058.2</v>
+      </c>
+      <c r="K15" s="41" t="inlineStr">
+        <is>
+          <t>Invoice LC76SW004. VAT-incl (excl R13,094.09 ×1.15).</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="41" t="inlineStr">
+        <is>
+          <t>Manjaro build — Fitment labour</t>
+        </is>
+      </c>
+      <c r="B16" s="41" t="inlineStr">
+        <is>
+          <t>Manjaro build</t>
+        </is>
+      </c>
+      <c r="C16" s="41" t="inlineStr">
+        <is>
+          <t>Manjaro Industries</t>
+        </is>
+      </c>
+      <c r="D16" s="42" t="n">
+        <v>46240</v>
+      </c>
+      <c r="E16" s="43" t="n">
+        <v>311263</v>
+      </c>
+      <c r="F16" s="41" t="inlineStr">
+        <is>
+          <t>LC76SW004</t>
+        </is>
+      </c>
+      <c r="G16" s="41" t="inlineStr">
+        <is>
+          <t>Permanent</t>
+        </is>
+      </c>
+      <c r="H16" s="41" t="inlineStr">
+        <is>
+          <t>Fitted</t>
+        </is>
+      </c>
+      <c r="I16" s="41" t="inlineStr">
+        <is>
+          <t>Cost</t>
+        </is>
+      </c>
+      <c r="J16" s="44" t="n">
+        <v>52008.75</v>
+      </c>
+      <c r="K16" s="41" t="inlineStr">
+        <is>
+          <t>Invoice LC76SW004. VAT-incl (excl R45,225.00 ×1.15).</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="41" t="inlineStr">
+        <is>
+          <t>ARB front bumper (black, winch-compatible)</t>
+        </is>
+      </c>
+      <c r="B17" s="41" t="inlineStr">
+        <is>
+          <t>Body &amp; armour</t>
+        </is>
+      </c>
+      <c r="C17" s="41" t="inlineStr"/>
+      <c r="D17" s="42" t="n">
+        <v>40219</v>
+      </c>
+      <c r="E17" s="43" t="inlineStr"/>
+      <c r="F17" s="41" t="inlineStr"/>
+      <c r="G17" s="41" t="inlineStr">
+        <is>
+          <t>Permanent</t>
+        </is>
+      </c>
+      <c r="H17" s="41" t="inlineStr">
+        <is>
+          <t>Fitted</t>
+        </is>
+      </c>
+      <c r="I17" s="41" t="inlineStr">
+        <is>
+          <t>Cost</t>
+        </is>
+      </c>
+      <c r="J17" s="44" t="n">
+        <v>10395</v>
+      </c>
+      <c r="K17" s="41" t="inlineStr">
+        <is>
+          <t>Original build ~2010–2012 (approx). Source: owner insurance-detail schedule (at cost).</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="41" t="inlineStr">
+        <is>
+          <t>Safari snorkel</t>
+        </is>
+      </c>
+      <c r="B18" s="41" t="inlineStr">
+        <is>
+          <t>Body &amp; armour</t>
+        </is>
+      </c>
+      <c r="C18" s="41" t="inlineStr"/>
+      <c r="D18" s="42" t="n">
+        <v>40219</v>
+      </c>
+      <c r="E18" s="43" t="inlineStr"/>
+      <c r="F18" s="41" t="inlineStr"/>
+      <c r="G18" s="41" t="inlineStr">
+        <is>
+          <t>Permanent</t>
+        </is>
+      </c>
+      <c r="H18" s="41" t="inlineStr">
+        <is>
+          <t>Fitted</t>
+        </is>
+      </c>
+      <c r="I18" s="41" t="inlineStr">
+        <is>
+          <t>Cost</t>
+        </is>
+      </c>
+      <c r="J18" s="44" t="n">
+        <v>4210</v>
+      </c>
+      <c r="K18" s="41" t="inlineStr">
+        <is>
+          <t>Original build ~2010–2012 (approx). Source: owner insurance-detail schedule (at cost).</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="41" t="inlineStr">
+        <is>
+          <t>T-Max 9500 electric winch</t>
+        </is>
+      </c>
+      <c r="B19" s="41" t="inlineStr">
+        <is>
+          <t>Recovery &amp; armour</t>
+        </is>
+      </c>
+      <c r="C19" s="41" t="inlineStr"/>
+      <c r="D19" s="42" t="n">
+        <v>40219</v>
+      </c>
+      <c r="E19" s="43" t="inlineStr"/>
+      <c r="F19" s="41" t="inlineStr"/>
+      <c r="G19" s="41" t="inlineStr">
+        <is>
+          <t>Permanent</t>
+        </is>
+      </c>
+      <c r="H19" s="41" t="inlineStr">
+        <is>
+          <t>Fitted</t>
+        </is>
+      </c>
+      <c r="I19" s="41" t="inlineStr">
+        <is>
+          <t>Cost</t>
+        </is>
+      </c>
+      <c r="J19" s="44" t="n">
+        <v>5465</v>
+      </c>
+      <c r="K19" s="41" t="inlineStr">
+        <is>
+          <t>Original build ~2010–2012 (approx). Source: owner insurance-detail schedule (at cost).</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="41" t="inlineStr">
+        <is>
+          <t>Replacement 145L long-range fuel tank</t>
+        </is>
+      </c>
+      <c r="B20" s="41" t="inlineStr">
+        <is>
+          <t>Fuel system</t>
+        </is>
+      </c>
+      <c r="C20" s="41" t="inlineStr"/>
+      <c r="D20" s="42" t="n">
+        <v>40219</v>
+      </c>
+      <c r="E20" s="43" t="inlineStr"/>
+      <c r="F20" s="41" t="inlineStr"/>
+      <c r="G20" s="41" t="inlineStr">
+        <is>
+          <t>Permanent</t>
+        </is>
+      </c>
+      <c r="H20" s="41" t="inlineStr">
+        <is>
+          <t>Fitted</t>
+        </is>
+      </c>
+      <c r="I20" s="41" t="inlineStr">
+        <is>
+          <t>Cost</t>
+        </is>
+      </c>
+      <c r="J20" s="44" t="n">
+        <v>6760</v>
+      </c>
+      <c r="K20" s="41" t="inlineStr">
+        <is>
+          <t>Original build ~2010–2012 (approx). Source: owner insurance-detail schedule (at cost).</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="41" t="inlineStr">
+        <is>
+          <t>AOP roof rack + top rail</t>
+        </is>
+      </c>
+      <c r="B21" s="41" t="inlineStr">
+        <is>
+          <t>Body &amp; armour</t>
+        </is>
+      </c>
+      <c r="C21" s="41" t="inlineStr"/>
+      <c r="D21" s="42" t="n">
+        <v>40219</v>
+      </c>
+      <c r="E21" s="43" t="inlineStr"/>
+      <c r="F21" s="41" t="inlineStr"/>
+      <c r="G21" s="41" t="inlineStr">
+        <is>
+          <t>Permanent</t>
+        </is>
+      </c>
+      <c r="H21" s="41" t="inlineStr">
+        <is>
+          <t>Fitted</t>
+        </is>
+      </c>
+      <c r="I21" s="41" t="inlineStr">
+        <is>
+          <t>Cost</t>
+        </is>
+      </c>
+      <c r="J21" s="44" t="n">
+        <v>7390</v>
+      </c>
+      <c r="K21" s="41" t="inlineStr">
+        <is>
+          <t>Original build ~2010–2012 (approx). Source: owner insurance-detail schedule (at cost).</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="41" t="inlineStr">
+        <is>
+          <t>AOP roof rack ladder</t>
+        </is>
+      </c>
+      <c r="B22" s="41" t="inlineStr">
+        <is>
+          <t>Body &amp; armour</t>
+        </is>
+      </c>
+      <c r="C22" s="41" t="inlineStr"/>
+      <c r="D22" s="42" t="n">
+        <v>40219</v>
+      </c>
+      <c r="E22" s="43" t="inlineStr"/>
+      <c r="F22" s="41" t="inlineStr"/>
+      <c r="G22" s="41" t="inlineStr">
+        <is>
+          <t>Permanent</t>
+        </is>
+      </c>
+      <c r="H22" s="41" t="inlineStr">
+        <is>
+          <t>Fitted</t>
+        </is>
+      </c>
+      <c r="I22" s="41" t="inlineStr">
+        <is>
+          <t>Cost</t>
+        </is>
+      </c>
+      <c r="J22" s="44" t="n">
+        <v>1460</v>
+      </c>
+      <c r="K22" s="41" t="inlineStr">
+        <is>
+          <t>Original build ~2010–2012 (approx). Source: owner insurance-detail schedule (at cost).</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="41" t="inlineStr">
+        <is>
+          <t>Escape Canvas seat covers (full set)</t>
+        </is>
+      </c>
+      <c r="B23" s="41" t="inlineStr">
+        <is>
+          <t>Interior</t>
+        </is>
+      </c>
+      <c r="C23" s="41" t="inlineStr"/>
+      <c r="D23" s="42" t="n">
+        <v>40219</v>
+      </c>
+      <c r="E23" s="43" t="inlineStr"/>
+      <c r="F23" s="41" t="inlineStr"/>
+      <c r="G23" s="41" t="inlineStr">
+        <is>
+          <t>Permanent</t>
+        </is>
+      </c>
+      <c r="H23" s="41" t="inlineStr">
+        <is>
+          <t>Fitted</t>
+        </is>
+      </c>
+      <c r="I23" s="41" t="inlineStr">
+        <is>
+          <t>Cost</t>
+        </is>
+      </c>
+      <c r="J23" s="44" t="n">
+        <v>3295</v>
+      </c>
+      <c r="K23" s="41" t="inlineStr">
+        <is>
+          <t>Original build ~2010–2012 (approx). Source: owner insurance-detail schedule (at cost).</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="41" t="inlineStr">
+        <is>
+          <t>ARB compressor (engine-bay mounted)</t>
+        </is>
+      </c>
+      <c r="B24" s="41" t="inlineStr">
+        <is>
+          <t>Recovery &amp; armour</t>
+        </is>
+      </c>
+      <c r="C24" s="41" t="inlineStr"/>
+      <c r="D24" s="42" t="n">
+        <v>40219</v>
+      </c>
+      <c r="E24" s="43" t="inlineStr"/>
+      <c r="F24" s="41" t="inlineStr"/>
+      <c r="G24" s="41" t="inlineStr">
+        <is>
+          <t>Permanent</t>
+        </is>
+      </c>
+      <c r="H24" s="41" t="inlineStr">
+        <is>
+          <t>Fitted</t>
+        </is>
+      </c>
+      <c r="I24" s="41" t="inlineStr">
+        <is>
+          <t>Cost</t>
+        </is>
+      </c>
+      <c r="J24" s="44" t="n">
+        <v>2850</v>
+      </c>
+      <c r="K24" s="41" t="inlineStr">
+        <is>
+          <t>Original build ~2010–2012 (approx). Source: owner insurance-detail schedule (at cost).</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="41" t="inlineStr">
+        <is>
+          <t>Complete OME medium suspension (ORIGINAL build)</t>
+        </is>
+      </c>
+      <c r="B25" s="41" t="inlineStr">
+        <is>
+          <t>Suspension</t>
+        </is>
+      </c>
+      <c r="C25" s="41" t="inlineStr"/>
+      <c r="D25" s="42" t="n">
+        <v>40219</v>
+      </c>
+      <c r="E25" s="43" t="inlineStr"/>
+      <c r="F25" s="41" t="inlineStr"/>
+      <c r="G25" s="41" t="inlineStr">
+        <is>
+          <t>Permanent</t>
+        </is>
+      </c>
+      <c r="H25" s="41" t="inlineStr">
+        <is>
+          <t>Fitted</t>
+        </is>
+      </c>
+      <c r="I25" s="41" t="inlineStr">
+        <is>
+          <t>Cost</t>
+        </is>
+      </c>
+      <c r="J25" s="44" t="n">
+        <v>18340</v>
+      </c>
+      <c r="K25" s="41" t="inlineStr">
+        <is>
+          <t>Original build ~2010–2012 (approx). Source: owner insurance-detail schedule (at cost).</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="41" t="inlineStr">
+        <is>
+          <t>SAC low-boost turbo kit</t>
+        </is>
+      </c>
+      <c r="B26" s="41" t="inlineStr">
+        <is>
+          <t>Engine &amp; powertrain</t>
+        </is>
+      </c>
+      <c r="C26" s="41" t="inlineStr"/>
+      <c r="D26" s="42" t="n">
+        <v>40219</v>
+      </c>
+      <c r="E26" s="43" t="inlineStr"/>
+      <c r="F26" s="41" t="inlineStr"/>
+      <c r="G26" s="41" t="inlineStr">
+        <is>
+          <t>Permanent</t>
+        </is>
+      </c>
+      <c r="H26" s="41" t="inlineStr">
+        <is>
+          <t>Fitted</t>
+        </is>
+      </c>
+      <c r="I26" s="41" t="inlineStr">
+        <is>
+          <t>Cost</t>
+        </is>
+      </c>
+      <c r="J26" s="44" t="n">
+        <v>17500</v>
+      </c>
+      <c r="K26" s="41" t="inlineStr">
+        <is>
+          <t>Original build ~2010–2012 (approx). Source: owner insurance-detail schedule (at cost).</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="41" t="inlineStr">
+        <is>
+          <t>EGT pyrometer gauge</t>
+        </is>
+      </c>
+      <c r="B27" s="41" t="inlineStr">
+        <is>
+          <t>Engine &amp; powertrain</t>
+        </is>
+      </c>
+      <c r="C27" s="41" t="inlineStr"/>
+      <c r="D27" s="42" t="n">
+        <v>40219</v>
+      </c>
+      <c r="E27" s="43" t="inlineStr"/>
+      <c r="F27" s="41" t="inlineStr"/>
+      <c r="G27" s="41" t="inlineStr">
+        <is>
+          <t>Permanent</t>
+        </is>
+      </c>
+      <c r="H27" s="41" t="inlineStr">
+        <is>
+          <t>Fitted</t>
+        </is>
+      </c>
+      <c r="I27" s="41" t="inlineStr">
+        <is>
+          <t>Cost</t>
+        </is>
+      </c>
+      <c r="J27" s="44" t="n">
+        <v>2500</v>
+      </c>
+      <c r="K27" s="41" t="inlineStr">
+        <is>
+          <t>Original build ~2010–2012 (approx). Source: owner insurance-detail schedule (at cost).</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="41" t="inlineStr">
+        <is>
+          <t>SAC intercooler + bonnet scoop</t>
+        </is>
+      </c>
+      <c r="B28" s="41" t="inlineStr">
+        <is>
+          <t>Engine &amp; powertrain</t>
+        </is>
+      </c>
+      <c r="C28" s="41" t="inlineStr"/>
+      <c r="D28" s="42" t="n">
+        <v>40219</v>
+      </c>
+      <c r="E28" s="43" t="inlineStr"/>
+      <c r="F28" s="41" t="inlineStr"/>
+      <c r="G28" s="41" t="inlineStr">
+        <is>
+          <t>Permanent</t>
+        </is>
+      </c>
+      <c r="H28" s="41" t="inlineStr">
+        <is>
+          <t>Fitted</t>
+        </is>
+      </c>
+      <c r="I28" s="41" t="inlineStr">
+        <is>
+          <t>Cost</t>
+        </is>
+      </c>
+      <c r="J28" s="44" t="n">
+        <v>13645</v>
+      </c>
+      <c r="K28" s="41" t="inlineStr">
+        <is>
+          <t>Original build ~2010–2012 (approx). Source: owner insurance-detail schedule (at cost).</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="41" t="inlineStr">
+        <is>
+          <t>National Luna 52L aluminium fridge/freezer</t>
+        </is>
+      </c>
+      <c r="B29" s="41" t="inlineStr">
+        <is>
+          <t>Kitchen (portable)</t>
+        </is>
+      </c>
+      <c r="C29" s="41" t="inlineStr"/>
+      <c r="D29" s="42" t="n">
+        <v>40219</v>
+      </c>
+      <c r="E29" s="43" t="inlineStr"/>
+      <c r="F29" s="41" t="inlineStr"/>
+      <c r="G29" s="41" t="inlineStr">
+        <is>
+          <t>Removable</t>
+        </is>
+      </c>
+      <c r="H29" s="41" t="inlineStr">
+        <is>
+          <t>Fitted</t>
+        </is>
+      </c>
+      <c r="I29" s="41" t="inlineStr">
+        <is>
+          <t>Cost</t>
+        </is>
+      </c>
+      <c r="J29" s="44" t="n">
+        <v>7950</v>
+      </c>
+      <c r="K29" s="41" t="inlineStr">
+        <is>
+          <t>Original build ~2010–2012 (approx). Source: owner insurance-detail schedule (at cost).</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="41" t="inlineStr">
+        <is>
+          <t>OzTent RV4 + 2 side panels</t>
+        </is>
+      </c>
+      <c r="B30" s="41" t="inlineStr">
+        <is>
+          <t>Camping (portable)</t>
+        </is>
+      </c>
+      <c r="C30" s="41" t="inlineStr"/>
+      <c r="D30" s="42" t="n">
+        <v>40219</v>
+      </c>
+      <c r="E30" s="43" t="inlineStr"/>
+      <c r="F30" s="41" t="inlineStr"/>
+      <c r="G30" s="41" t="inlineStr">
+        <is>
+          <t>Removable</t>
+        </is>
+      </c>
+      <c r="H30" s="41" t="inlineStr">
+        <is>
+          <t>Fitted</t>
+        </is>
+      </c>
+      <c r="I30" s="41" t="inlineStr">
+        <is>
+          <t>Cost</t>
+        </is>
+      </c>
+      <c r="J30" s="44" t="n">
+        <v>7995</v>
+      </c>
+      <c r="K30" s="41" t="inlineStr">
+        <is>
+          <t>Original build ~2010–2012 (approx). Source: owner insurance-detail schedule (at cost).</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="41" t="inlineStr">
+        <is>
+          <t>MaxTrax recovery boards (×2)</t>
+        </is>
+      </c>
+      <c r="B31" s="41" t="inlineStr">
+        <is>
+          <t>Recovery (portable)</t>
+        </is>
+      </c>
+      <c r="C31" s="41" t="inlineStr"/>
+      <c r="D31" s="42" t="n">
+        <v>40219</v>
+      </c>
+      <c r="E31" s="43" t="inlineStr"/>
+      <c r="F31" s="41" t="inlineStr"/>
+      <c r="G31" s="41" t="inlineStr">
+        <is>
+          <t>Removable</t>
+        </is>
+      </c>
+      <c r="H31" s="41" t="inlineStr">
+        <is>
+          <t>Fitted</t>
+        </is>
+      </c>
+      <c r="I31" s="41" t="inlineStr">
+        <is>
+          <t>Cost</t>
+        </is>
+      </c>
+      <c r="J31" s="44" t="n">
+        <v>8600</v>
+      </c>
+      <c r="K31" s="41" t="inlineStr">
+        <is>
+          <t>Original build ~2010–2012 (approx). Source: owner insurance-detail schedule (at cost).</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="41" t="inlineStr">
+        <is>
+          <t>Indeflate 2-hose deflation/inflation unit</t>
+        </is>
+      </c>
+      <c r="B32" s="41" t="inlineStr">
+        <is>
+          <t>Recovery &amp; armour</t>
+        </is>
+      </c>
+      <c r="C32" s="41" t="inlineStr"/>
+      <c r="D32" s="41" t="inlineStr"/>
+      <c r="E32" s="43" t="inlineStr"/>
+      <c r="F32" s="41" t="inlineStr"/>
+      <c r="G32" s="41" t="inlineStr">
+        <is>
+          <t>Permanent</t>
+        </is>
+      </c>
+      <c r="H32" s="41" t="inlineStr">
+        <is>
+          <t>Fitted</t>
+        </is>
+      </c>
+      <c r="I32" s="41" t="inlineStr">
+        <is>
+          <t>Replacement</t>
+        </is>
+      </c>
+      <c r="J32" s="44" t="n">
+        <v>4500</v>
+      </c>
+      <c r="K32" s="41" t="inlineStr">
+        <is>
+          <t>Replacement value (no cost on record). Source: insurance valuation Doc B.</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="41" t="inlineStr">
+        <is>
+          <t>ARB hydraulic jack + tyre lift</t>
+        </is>
+      </c>
+      <c r="B33" s="41" t="inlineStr">
+        <is>
+          <t>Recovery &amp; armour</t>
+        </is>
+      </c>
+      <c r="C33" s="41" t="inlineStr"/>
+      <c r="D33" s="41" t="inlineStr"/>
+      <c r="E33" s="43" t="inlineStr"/>
+      <c r="F33" s="41" t="inlineStr"/>
+      <c r="G33" s="41" t="inlineStr">
+        <is>
+          <t>Permanent</t>
+        </is>
+      </c>
+      <c r="H33" s="41" t="inlineStr">
+        <is>
+          <t>Fitted</t>
+        </is>
+      </c>
+      <c r="I33" s="41" t="inlineStr">
+        <is>
+          <t>Replacement</t>
+        </is>
+      </c>
+      <c r="J33" s="44" t="n">
+        <v>28995</v>
+      </c>
+      <c r="K33" s="41" t="inlineStr">
+        <is>
+          <t>Replacement value (no cost on record). Source: insurance valuation Doc B.</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="41" t="inlineStr">
+        <is>
+          <t>ARB tyre repair kit</t>
+        </is>
+      </c>
+      <c r="B34" s="41" t="inlineStr">
+        <is>
+          <t>Recovery &amp; armour</t>
+        </is>
+      </c>
+      <c r="C34" s="41" t="inlineStr"/>
+      <c r="D34" s="41" t="inlineStr"/>
+      <c r="E34" s="43" t="inlineStr"/>
+      <c r="F34" s="41" t="inlineStr"/>
+      <c r="G34" s="41" t="inlineStr">
+        <is>
+          <t>Permanent</t>
+        </is>
+      </c>
+      <c r="H34" s="41" t="inlineStr">
+        <is>
+          <t>Fitted</t>
+        </is>
+      </c>
+      <c r="I34" s="41" t="inlineStr">
+        <is>
+          <t>Replacement</t>
+        </is>
+      </c>
+      <c r="J34" s="44" t="n">
+        <v>1200</v>
+      </c>
+      <c r="K34" s="41" t="inlineStr">
+        <is>
+          <t>Replacement value (no cost on record). Source: insurance valuation Doc B.</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="41" t="inlineStr">
+        <is>
+          <t>Heavy-duty jumper cables</t>
+        </is>
+      </c>
+      <c r="B35" s="41" t="inlineStr">
+        <is>
+          <t>Recovery &amp; armour</t>
+        </is>
+      </c>
+      <c r="C35" s="41" t="inlineStr"/>
+      <c r="D35" s="41" t="inlineStr"/>
+      <c r="E35" s="43" t="inlineStr"/>
+      <c r="F35" s="41" t="inlineStr"/>
+      <c r="G35" s="41" t="inlineStr">
+        <is>
+          <t>Permanent</t>
+        </is>
+      </c>
+      <c r="H35" s="41" t="inlineStr">
+        <is>
+          <t>Fitted</t>
+        </is>
+      </c>
+      <c r="I35" s="41" t="inlineStr">
+        <is>
+          <t>Replacement</t>
+        </is>
+      </c>
+      <c r="J35" s="44" t="n">
+        <v>1500</v>
+      </c>
+      <c r="K35" s="41" t="inlineStr">
+        <is>
+          <t>Replacement value (no cost on record). Source: insurance valuation Doc B.</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="41" t="inlineStr">
+        <is>
+          <t>Recovery PPE (spade, gloves, glasses)</t>
+        </is>
+      </c>
+      <c r="B36" s="41" t="inlineStr">
+        <is>
+          <t>Recovery &amp; armour</t>
+        </is>
+      </c>
+      <c r="C36" s="41" t="inlineStr"/>
+      <c r="D36" s="41" t="inlineStr"/>
+      <c r="E36" s="43" t="inlineStr"/>
+      <c r="F36" s="41" t="inlineStr"/>
+      <c r="G36" s="41" t="inlineStr">
+        <is>
+          <t>Permanent</t>
+        </is>
+      </c>
+      <c r="H36" s="41" t="inlineStr">
+        <is>
+          <t>Fitted</t>
+        </is>
+      </c>
+      <c r="I36" s="41" t="inlineStr">
+        <is>
+          <t>Replacement</t>
+        </is>
+      </c>
+      <c r="J36" s="44" t="n">
+        <v>1000</v>
+      </c>
+      <c r="K36" s="41" t="inlineStr">
+        <is>
+          <t>Replacement value (no cost on record). Source: insurance valuation Doc B.</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="41" t="inlineStr">
+        <is>
+          <t>Hardkorr 200W portable solar blanket</t>
+        </is>
+      </c>
+      <c r="B37" s="41" t="inlineStr">
+        <is>
+          <t>Power (portable)</t>
+        </is>
+      </c>
+      <c r="C37" s="41" t="inlineStr"/>
+      <c r="D37" s="41" t="inlineStr"/>
+      <c r="E37" s="43" t="inlineStr"/>
+      <c r="F37" s="41" t="inlineStr"/>
+      <c r="G37" s="41" t="inlineStr">
+        <is>
+          <t>Removable</t>
+        </is>
+      </c>
+      <c r="H37" s="41" t="inlineStr">
+        <is>
+          <t>Fitted</t>
+        </is>
+      </c>
+      <c r="I37" s="41" t="inlineStr">
+        <is>
+          <t>Replacement</t>
+        </is>
+      </c>
+      <c r="J37" s="44" t="n">
+        <v>7725</v>
+      </c>
+      <c r="K37" s="41" t="inlineStr">
+        <is>
+          <t>Replacement value (no cost on record). Source: insurance valuation Doc B.</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="41" t="inlineStr">
+        <is>
+          <t>ARB portable jump starter</t>
+        </is>
+      </c>
+      <c r="B38" s="41" t="inlineStr">
+        <is>
+          <t>Power (portable)</t>
+        </is>
+      </c>
+      <c r="C38" s="41" t="inlineStr"/>
+      <c r="D38" s="41" t="inlineStr"/>
+      <c r="E38" s="43" t="inlineStr"/>
+      <c r="F38" s="41" t="inlineStr"/>
+      <c r="G38" s="41" t="inlineStr">
+        <is>
+          <t>Removable</t>
+        </is>
+      </c>
+      <c r="H38" s="41" t="inlineStr">
+        <is>
+          <t>Fitted</t>
+        </is>
+      </c>
+      <c r="I38" s="41" t="inlineStr">
+        <is>
+          <t>Replacement</t>
+        </is>
+      </c>
+      <c r="J38" s="44" t="n">
+        <v>4000</v>
+      </c>
+      <c r="K38" s="41" t="inlineStr">
+        <is>
+          <t>Replacement value (no cost on record). Source: insurance valuation Doc B.</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="41" t="inlineStr">
+        <is>
+          <t>5L gas bottle + twin-top cast-iron cooker</t>
+        </is>
+      </c>
+      <c r="B39" s="41" t="inlineStr">
+        <is>
+          <t>Kitchen (portable)</t>
+        </is>
+      </c>
+      <c r="C39" s="41" t="inlineStr"/>
+      <c r="D39" s="41" t="inlineStr"/>
+      <c r="E39" s="43" t="inlineStr"/>
+      <c r="F39" s="41" t="inlineStr"/>
+      <c r="G39" s="41" t="inlineStr">
+        <is>
+          <t>Removable</t>
+        </is>
+      </c>
+      <c r="H39" s="41" t="inlineStr">
+        <is>
+          <t>Fitted</t>
+        </is>
+      </c>
+      <c r="I39" s="41" t="inlineStr">
+        <is>
+          <t>Replacement</t>
+        </is>
+      </c>
+      <c r="J39" s="44" t="n">
+        <v>2000</v>
+      </c>
+      <c r="K39" s="41" t="inlineStr">
+        <is>
+          <t>Replacement value (no cost on record). Source: insurance valuation Doc B.</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="41" t="inlineStr">
+        <is>
+          <t>Aluminium table under roof rack</t>
+        </is>
+      </c>
+      <c r="B40" s="41" t="inlineStr">
+        <is>
+          <t>Kitchen (portable)</t>
+        </is>
+      </c>
+      <c r="C40" s="41" t="inlineStr"/>
+      <c r="D40" s="41" t="inlineStr"/>
+      <c r="E40" s="43" t="inlineStr"/>
+      <c r="F40" s="41" t="inlineStr"/>
+      <c r="G40" s="41" t="inlineStr">
+        <is>
+          <t>Removable</t>
+        </is>
+      </c>
+      <c r="H40" s="41" t="inlineStr">
+        <is>
+          <t>Fitted</t>
+        </is>
+      </c>
+      <c r="I40" s="41" t="inlineStr">
+        <is>
+          <t>Replacement</t>
+        </is>
+      </c>
+      <c r="J40" s="44" t="n">
+        <v>2500</v>
+      </c>
+      <c r="K40" s="41" t="inlineStr">
+        <is>
+          <t>Replacement value (no cost on record). Source: insurance valuation Doc B.</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="41" t="inlineStr">
+        <is>
+          <t>Desert Fox collapsible water cells 20L (×2)</t>
+        </is>
+      </c>
+      <c r="B41" s="41" t="inlineStr">
+        <is>
+          <t>Water (portable)</t>
+        </is>
+      </c>
+      <c r="C41" s="41" t="inlineStr"/>
+      <c r="D41" s="41" t="inlineStr"/>
+      <c r="E41" s="43" t="inlineStr"/>
+      <c r="F41" s="41" t="inlineStr"/>
+      <c r="G41" s="41" t="inlineStr">
+        <is>
+          <t>Removable</t>
+        </is>
+      </c>
+      <c r="H41" s="41" t="inlineStr">
+        <is>
+          <t>Fitted</t>
+        </is>
+      </c>
+      <c r="I41" s="41" t="inlineStr">
+        <is>
+          <t>Replacement</t>
+        </is>
+      </c>
+      <c r="J41" s="44" t="n">
+        <v>3000</v>
+      </c>
+      <c r="K41" s="41" t="inlineStr">
+        <is>
+          <t>Replacement value (no cost on record). Source: insurance valuation Doc B.</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="41" t="inlineStr">
+        <is>
+          <t>Desert Fox collapsible fuel cells 20L (×2)</t>
+        </is>
+      </c>
+      <c r="B42" s="41" t="inlineStr">
+        <is>
+          <t>Fuel (portable)</t>
+        </is>
+      </c>
+      <c r="C42" s="41" t="inlineStr"/>
+      <c r="D42" s="41" t="inlineStr"/>
+      <c r="E42" s="43" t="inlineStr"/>
+      <c r="F42" s="41" t="inlineStr"/>
+      <c r="G42" s="41" t="inlineStr">
+        <is>
+          <t>Removable</t>
+        </is>
+      </c>
+      <c r="H42" s="41" t="inlineStr">
+        <is>
+          <t>Fitted</t>
+        </is>
+      </c>
+      <c r="I42" s="41" t="inlineStr">
+        <is>
+          <t>Replacement</t>
+        </is>
+      </c>
+      <c r="J42" s="44" t="n">
+        <v>4000</v>
+      </c>
+      <c r="K42" s="41" t="inlineStr">
+        <is>
+          <t>Replacement value (no cost on record). Source: insurance valuation Doc B.</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="41" t="inlineStr">
+        <is>
+          <t>Recovery kit (shackles, kinetic rope, snatch strap, tree protector, pulley block, dampener)</t>
+        </is>
+      </c>
+      <c r="B43" s="41" t="inlineStr">
+        <is>
+          <t>Recovery (portable)</t>
+        </is>
+      </c>
+      <c r="C43" s="41" t="inlineStr"/>
+      <c r="D43" s="41" t="inlineStr"/>
+      <c r="E43" s="43" t="inlineStr"/>
+      <c r="F43" s="41" t="inlineStr"/>
+      <c r="G43" s="41" t="inlineStr">
+        <is>
+          <t>Removable</t>
+        </is>
+      </c>
+      <c r="H43" s="41" t="inlineStr">
+        <is>
+          <t>Fitted</t>
+        </is>
+      </c>
+      <c r="I43" s="41" t="inlineStr">
+        <is>
+          <t>Replacement</t>
+        </is>
+      </c>
+      <c r="J43" s="44" t="n">
+        <v>8000</v>
+      </c>
+      <c r="K43" s="41" t="inlineStr">
+        <is>
+          <t>Replacement value (no cost on record). Source: insurance valuation Doc B.</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="41" t="inlineStr">
+        <is>
+          <t>T-Max portable compressor</t>
+        </is>
+      </c>
+      <c r="B44" s="41" t="inlineStr">
+        <is>
+          <t>Recovery (portable)</t>
+        </is>
+      </c>
+      <c r="C44" s="41" t="inlineStr"/>
+      <c r="D44" s="41" t="inlineStr"/>
+      <c r="E44" s="43" t="inlineStr"/>
+      <c r="F44" s="41" t="inlineStr"/>
+      <c r="G44" s="41" t="inlineStr">
+        <is>
+          <t>Removable</t>
+        </is>
+      </c>
+      <c r="H44" s="41" t="inlineStr">
+        <is>
+          <t>Fitted</t>
+        </is>
+      </c>
+      <c r="I44" s="41" t="inlineStr">
+        <is>
+          <t>Replacement</t>
+        </is>
+      </c>
+      <c r="J44" s="44" t="n">
+        <v>3500</v>
+      </c>
+      <c r="K44" s="41" t="inlineStr">
+        <is>
+          <t>Replacement value (no cost on record). Source: insurance valuation Doc B.</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="41" t="inlineStr">
+        <is>
+          <t>SecureTech radiator seed net (800×1000mm)</t>
+        </is>
+      </c>
+      <c r="B45" s="41" t="inlineStr">
+        <is>
+          <t>Recovery (portable)</t>
+        </is>
+      </c>
+      <c r="C45" s="41" t="inlineStr"/>
+      <c r="D45" s="41" t="inlineStr"/>
+      <c r="E45" s="43" t="inlineStr"/>
+      <c r="F45" s="41" t="inlineStr"/>
+      <c r="G45" s="41" t="inlineStr">
+        <is>
+          <t>Removable</t>
+        </is>
+      </c>
+      <c r="H45" s="41" t="inlineStr">
+        <is>
+          <t>Fitted</t>
+        </is>
+      </c>
+      <c r="I45" s="41" t="inlineStr">
+        <is>
+          <t>Replacement</t>
+        </is>
+      </c>
+      <c r="J45" s="44" t="n">
+        <v>1500</v>
+      </c>
+      <c r="K45" s="41" t="inlineStr">
+        <is>
+          <t>Replacement value (no cost on record). Source: insurance valuation Doc B.</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="41" t="inlineStr">
+        <is>
+          <t>DEFA SmartCharge portable mains battery charger</t>
+        </is>
+      </c>
+      <c r="B46" s="41" t="inlineStr">
+        <is>
+          <t>Power (portable)</t>
+        </is>
+      </c>
+      <c r="C46" s="41" t="inlineStr"/>
+      <c r="D46" s="41" t="inlineStr"/>
+      <c r="E46" s="43" t="inlineStr"/>
+      <c r="F46" s="41" t="inlineStr"/>
+      <c r="G46" s="41" t="inlineStr">
+        <is>
+          <t>Removable</t>
+        </is>
+      </c>
+      <c r="H46" s="41" t="inlineStr">
+        <is>
+          <t>Fitted</t>
+        </is>
+      </c>
+      <c r="I46" s="41" t="inlineStr">
+        <is>
+          <t>Replacement</t>
+        </is>
+      </c>
+      <c r="J46" s="44" t="n">
+        <v>3500</v>
+      </c>
+      <c r="K46" s="41" t="inlineStr">
+        <is>
+          <t>Replacement value (no cost on record). Source: insurance valuation Doc B.</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="45" t="inlineStr">
+        <is>
+          <t>CONVENTION: Master of fitted kit &amp; acquisition cost — separate from Services (maintenance/repair). Insurance valuation is the derived VALUE view (filters this sheet by Fitment type / Status). Basis: Cost = actual invoice amount (VAT-incl). Replacement = current replacement value where no cost is on record (flagged). Status Removed-superseded excluded from insurance value. Original tow bar removed; replacement GobiX hitch is part of the Manjaro rear-bumper build (Rear row). DEFA SmartCharge retained as a portable spare (backup to shore-power-via-MultiPlus). Reclassification 2026-08-06.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/LC_Service_history_FINAL.xlsx
+++ b/LC_Service_history_FINAL.xlsx
@@ -11614,10 +11614,51 @@
         </is>
       </c>
     </row>
+    <row r="47">
+      <c r="A47" s="41" t="inlineStr">
+        <is>
+          <t>Toyota Land Cruiser 76 Series SW — base vehicle (original purchase)</t>
+        </is>
+      </c>
+      <c r="B47" s="41" t="inlineStr">
+        <is>
+          <t>Base vehicle</t>
+        </is>
+      </c>
+      <c r="C47" s="41" t="n"/>
+      <c r="D47" s="42" t="n">
+        <v>40219</v>
+      </c>
+      <c r="E47" s="43" t="n"/>
+      <c r="F47" s="41" t="n"/>
+      <c r="G47" s="41" t="inlineStr">
+        <is>
+          <t>Base vehicle</t>
+        </is>
+      </c>
+      <c r="H47" s="41" t="inlineStr">
+        <is>
+          <t>Fitted</t>
+        </is>
+      </c>
+      <c r="I47" s="41" t="inlineStr">
+        <is>
+          <t>Cost</t>
+        </is>
+      </c>
+      <c r="J47" s="44" t="n">
+        <v>394000</v>
+      </c>
+      <c r="K47" s="41" t="inlineStr">
+        <is>
+          <t>Original vehicle purchase, 10 Feb 2010. Historical acquisition cost. Base vehicle is insured at agreed value (separate exercise), NOT this purchase cost; excluded from the accessory/build insurance schedule and from the build &amp; kit subtotal. Included in Total cost of vehicle.</t>
+        </is>
+      </c>
+    </row>
     <row r="48">
       <c r="A48" s="45" t="inlineStr">
         <is>
-          <t>CONVENTION: Master of fitted kit &amp; acquisition cost — separate from Services (maintenance/repair). Insurance valuation is the derived VALUE view (filters this sheet by Fitment type / Status). Basis: Cost = actual invoice amount (VAT-incl). Replacement = current replacement value where no cost is on record (flagged). Status Removed-superseded excluded from insurance value. Original tow bar removed; replacement GobiX hitch is part of the Manjaro rear-bumper build (Rear row). DEFA SmartCharge retained as a portable spare (backup to shore-power-via-MultiPlus). Reclassification 2026-08-06.</t>
+          <t>CONVENTION: Master of fitted kit &amp; acquisition cost — separate from Services (maintenance/repair). Insurance valuation is the derived VALUE view (filters this sheet by Fitment type / Status). Basis: Cost = actual invoice amount (VAT-incl). Replacement = current replacement value where no cost is on record (flagged). Status Removed-superseded excluded from insurance value. Original tow bar removed; replacement GobiX hitch is part of the Manjaro rear-bumper build (Rear row). DEFA SmartCharge retained as a portable spare (backup to shore-power-via-MultiPlus). Reclassification 2026-08-06. ROW ADDED 2026-08-06: base vehicle (original purchase 10 Feb 2010, R394,000) as Fitment type "Base vehicle" — build &amp; kit subtotal (45 rows) R544,082.76; TOTAL COST OF VEHICLE (46 rows, base + build &amp; kit) R938,082.76. Base vehicle excluded from the insurance accessory schedule (insured at agreed value, not purchase cost).</t>
         </is>
       </c>
     </row>

--- a/LC_Service_history_FINAL.xlsx
+++ b/LC_Service_history_FINAL.xlsx
@@ -9600,7 +9600,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K48"/>
+  <dimension ref="A1:K49"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="46" customWidth="1" min="1" max="1"/>
@@ -11656,9 +11656,60 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="45" t="inlineStr">
-        <is>
-          <t>CONVENTION: Master of fitted kit &amp; acquisition cost — separate from Services (maintenance/repair). Insurance valuation is the derived VALUE view (filters this sheet by Fitment type / Status). Basis: Cost = actual invoice amount (VAT-incl). Replacement = current replacement value where no cost is on record (flagged). Status Removed-superseded excluded from insurance value. Original tow bar removed; replacement GobiX hitch is part of the Manjaro rear-bumper build (Rear row). DEFA SmartCharge retained as a portable spare (backup to shore-power-via-MultiPlus). Reclassification 2026-08-06. ROW ADDED 2026-08-06: base vehicle (original purchase 10 Feb 2010, R394,000) as Fitment type "Base vehicle" — build &amp; kit subtotal (45 rows) R544,082.76; TOTAL COST OF VEHICLE (46 rows, base + build &amp; kit) R938,082.76. Base vehicle excluded from the insurance accessory schedule (insured at agreed value, not purchase cost).</t>
+      <c r="A48" s="41" t="inlineStr">
+        <is>
+          <t>Inmarsat IsatPhone 2.1 satellite phone + hardcase</t>
+        </is>
+      </c>
+      <c r="B48" s="41" t="inlineStr">
+        <is>
+          <t>Comms (portable)</t>
+        </is>
+      </c>
+      <c r="C48" s="41" t="inlineStr">
+        <is>
+          <t>Global Sat4Rent</t>
+        </is>
+      </c>
+      <c r="D48" s="42" t="n">
+        <v>46240</v>
+      </c>
+      <c r="E48" s="43" t="n">
+        <v>311263</v>
+      </c>
+      <c r="F48" s="41" t="inlineStr">
+        <is>
+          <t>Invoice 8984</t>
+        </is>
+      </c>
+      <c r="G48" s="41" t="inlineStr">
+        <is>
+          <t>Removable</t>
+        </is>
+      </c>
+      <c r="H48" s="41" t="inlineStr">
+        <is>
+          <t>Fitted</t>
+        </is>
+      </c>
+      <c r="I48" s="41" t="inlineStr">
+        <is>
+          <t>Cost</t>
+        </is>
+      </c>
+      <c r="J48" s="44" t="n">
+        <v>21924.25</v>
+      </c>
+      <c r="K48" s="41" t="inlineStr">
+        <is>
+          <t>IsatPhone Pro Prepay Regional Plan 2018, 20 units, expires 7 Aug 2027. MSISDN +870 777 751 134. ICC ID 898709925417152692. Not insured under motor policy — recorded for completeness.</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="45" t="inlineStr">
+        <is>
+          <t>CONVENTION: Master of fitted kit &amp; acquisition cost — separate from Services (maintenance/repair). Insurance valuation is the derived VALUE view (filters this sheet by Fitment type / Status). Basis: Cost = actual invoice amount (VAT-incl). Replacement = current replacement value where no cost is on record (flagged). Status Removed-superseded excluded from insurance value. Original tow bar removed; replacement GobiX hitch is part of the Manjaro rear-bumper build (Rear row). DEFA SmartCharge retained as a portable spare (backup to shore-power-via-MultiPlus). Reclassification 2026-08-06. ROW ADDED 2026-08-06: base vehicle (original purchase 10 Feb 2010, R394,000) as Fitment type "Base vehicle" — build &amp; kit subtotal (45 rows) R544,082.76; TOTAL COST OF VEHICLE (46 rows, base + build &amp; kit) R938,082.76. Base vehicle excluded from the insurance accessory schedule (insured at agreed value, not purchase cost). ROW ADDED 2026-08-07: Inmarsat IsatPhone 2.1 (Global Sat4Rent, invoice 8984, R21,924.25 incl. VAT, 6 Aug 2026 @ 311,263 km) as Removable/Fitted/Cost. Satellite voice phone for emergency calls — not insured under motor policy, recorded as asset. 47 rows now.</t>
         </is>
       </c>
     </row>

--- a/LC_Service_history_FINAL.xlsx
+++ b/LC_Service_history_FINAL.xlsx
@@ -17,10 +17,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="3">
+  <numFmts count="2">
     <numFmt numFmtId="164" formatCode="&quot;R&quot;#,##0.00"/>
     <numFmt numFmtId="165" formatCode="&quot;R&quot;#,##0_);[Red]\(&quot;R&quot;#,##0\)"/>
-    <numFmt numFmtId="166" formatCode="yyyy-mm-dd h:mm:ss"/>
   </numFmts>
   <fonts count="8">
     <font>
@@ -10909,7 +10908,7 @@
     <row r="29">
       <c r="A29" s="41" t="inlineStr">
         <is>
-          <t>National Luna 52L aluminium fridge/freezer</t>
+          <t>National Luna 55L aluminium fridge/freezer</t>
         </is>
       </c>
       <c r="B29" s="41" t="inlineStr">
